--- a/output/yearly_surface_area_iteration_43_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_43_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497639233583</v>
+        <v>10.84497615976542</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907215139894</v>
+        <v>37.78907134101269</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.318528224532471</v>
+        <v>6.722026530977911</v>
       </c>
       <c r="C2" t="n">
-        <v>7.069565218281282</v>
+        <v>7.046003273379358</v>
       </c>
       <c r="D2" t="n">
-        <v>38.32153988756999</v>
+        <v>41.05178025308038</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.47082229187775</v>
+        <v>22.20222433154161</v>
       </c>
       <c r="C3" t="n">
-        <v>24.48969648243668</v>
+        <v>24.45533531278805</v>
       </c>
       <c r="D3" t="n">
-        <v>90.50241211599223</v>
+        <v>92.12720456652069</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.20631555327462</v>
+        <v>42.60195987808609</v>
       </c>
       <c r="C4" t="n">
-        <v>55.4795445146915</v>
+        <v>84.28500390499717</v>
       </c>
       <c r="D4" t="n">
-        <v>108.2789177967892</v>
+        <v>110.4996311037955</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.46812339513905</v>
+        <v>52.91620125890309</v>
       </c>
       <c r="C5" t="n">
-        <v>69.99861131279759</v>
+        <v>131.5787360616788</v>
       </c>
       <c r="D5" t="n">
-        <v>72.35480580298994</v>
+        <v>79.49702035138549</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.2806095836279</v>
+        <v>51.20010627187966</v>
       </c>
       <c r="C6" t="n">
-        <v>89.68068928753766</v>
+        <v>115.7637622939669</v>
       </c>
       <c r="D6" t="n">
-        <v>46.41015922285948</v>
+        <v>51.24035792775378</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.89015173477814</v>
+        <v>35.39298648580176</v>
       </c>
       <c r="C7" t="n">
-        <v>93.06379187637214</v>
+        <v>83.12261462316894</v>
       </c>
       <c r="D7" t="n">
-        <v>39.04606969330414</v>
+        <v>39.58504918293564</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.3600647277471</v>
+        <v>17.7745421853885</v>
       </c>
       <c r="C8" t="n">
-        <v>65.25676990128548</v>
+        <v>43.39324852770901</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.542186774651494</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>38.49530923122167</v>
+        <v>28.51093507903161</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.688289362795794</v>
+        <v>7.679908126032064</v>
       </c>
       <c r="C21" t="n">
-        <v>93.22050852389901</v>
+        <v>94.07887454389278</v>
       </c>
       <c r="D21" t="n">
-        <v>7.688289362795794</v>
+        <v>8.639896641786072</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.326783116793946</v>
+        <v>9.185231520933158</v>
       </c>
       <c r="C2" t="n">
-        <v>8.279078389913352</v>
+        <v>11.36078443354409</v>
       </c>
       <c r="D2" t="n">
-        <v>49.49088351878596</v>
+        <v>37.81986681069987</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.22047662729481</v>
+        <v>22.36912144126357</v>
       </c>
       <c r="C3" t="n">
-        <v>25.89359569950962</v>
+        <v>25.78069471352124</v>
       </c>
       <c r="D3" t="n">
-        <v>98.16986168615981</v>
+        <v>102.2048447506142</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.18529794085794</v>
+        <v>41.81067122846316</v>
       </c>
       <c r="C4" t="n">
-        <v>57.7257832620082</v>
+        <v>72.78579304515428</v>
       </c>
       <c r="D4" t="n">
-        <v>124.666250476077</v>
+        <v>125.891471610977</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.35860962061991</v>
+        <v>57.5304154688631</v>
       </c>
       <c r="C5" t="n">
-        <v>85.78020565856507</v>
+        <v>141.3225820263284</v>
       </c>
       <c r="D5" t="n">
-        <v>92.30882789180636</v>
+        <v>97.4875470317083</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.77370897306707</v>
+        <v>60.25672884355649</v>
       </c>
       <c r="C6" t="n">
-        <v>99.22033172970391</v>
+        <v>158.7927824234004</v>
       </c>
       <c r="D6" t="n">
-        <v>56.39256987964104</v>
+        <v>61.42402686390595</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.20872101703962</v>
+        <v>47.25053525769474</v>
       </c>
       <c r="C7" t="n">
-        <v>111.2094346939659</v>
+        <v>120.6715190674967</v>
       </c>
       <c r="D7" t="n">
-        <v>43.29801900039708</v>
+        <v>44.55563780953724</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.12354564648163</v>
+        <v>26.78698611037422</v>
       </c>
       <c r="C8" t="n">
-        <v>92.29410167624263</v>
+        <v>73.8519710519663</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.42343636016663</v>
+        <v>12.42499894494763</v>
       </c>
       <c r="C9" t="n">
-        <v>58.79687000734145</v>
+        <v>39.93749660876023</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>37.5813021185679</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1321,7 +1321,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.870264669734817</v>
+        <v>7.854477833619981</v>
       </c>
       <c r="C21" t="n">
-        <v>101.3296576228358</v>
+        <v>102.1082118370598</v>
       </c>
       <c r="D21" t="n">
-        <v>8.854047753451669</v>
+        <v>9.818097292024976</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.198975988792613</v>
+        <v>9.356055621472102</v>
       </c>
       <c r="C2" t="n">
-        <v>9.059567814789567</v>
+        <v>11.02600846639593</v>
       </c>
       <c r="D2" t="n">
-        <v>39.63119132503524</v>
+        <v>34.3179727496515</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.3445777486574</v>
+        <v>25.59907138823558</v>
       </c>
       <c r="C3" t="n">
-        <v>28.65230674844316</v>
+        <v>33.85066084243002</v>
       </c>
       <c r="D3" t="n">
-        <v>110.8344070709437</v>
+        <v>106.0876569209103</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.96007680595792</v>
+        <v>41.47884050442774</v>
       </c>
       <c r="C4" t="n">
-        <v>60.76331065894783</v>
+        <v>68.14016290865837</v>
       </c>
       <c r="D4" t="n">
-        <v>140.9259559538126</v>
+        <v>140.9897695545887</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.88031856220246</v>
+        <v>59.05212441044566</v>
       </c>
       <c r="C5" t="n">
-        <v>93.80599314078275</v>
+        <v>137.812833983646</v>
       </c>
       <c r="D5" t="n">
-        <v>109.8330244126119</v>
+        <v>115.3308115563941</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.18001365390501</v>
+        <v>66.93850371866029</v>
       </c>
       <c r="C6" t="n">
-        <v>114.435457650121</v>
+        <v>184.5940938387108</v>
       </c>
       <c r="D6" t="n">
-        <v>69.31335141523331</v>
+        <v>73.21776203502289</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>58.56910453995621</v>
+        <v>57.01205268102077</v>
       </c>
       <c r="C7" t="n">
-        <v>126.1212005737707</v>
+        <v>164.7480639973615</v>
       </c>
       <c r="D7" t="n">
-        <v>47.9691745772034</v>
+        <v>50.48441219548373</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>38.7201294554942</v>
+        <v>36.46701847424777</v>
       </c>
       <c r="C8" t="n">
-        <v>115.9100427018997</v>
+        <v>109.8182981970482</v>
       </c>
       <c r="D8" t="n">
-        <v>40.88979188187965</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.96874830438012</v>
+        <v>18.19374845510188</v>
       </c>
       <c r="C9" t="n">
-        <v>82.53749299143782</v>
+        <v>60.57186985661969</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.252972112526189</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="C10" t="n">
-        <v>51.53193699591508</v>
+        <v>38.29306920414684</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>37.13853390395258</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.036154857642231</v>
+        <v>8.012414965391846</v>
       </c>
       <c r="C21" t="n">
-        <v>109.4926099353754</v>
+        <v>109.1691539034639</v>
       </c>
       <c r="D21" t="n">
-        <v>10.04519357205279</v>
+        <v>11.01707057741379</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.322275288900212</v>
+        <v>8.672759219316323</v>
       </c>
       <c r="C2" t="n">
-        <v>6.160466844148735</v>
+        <v>7.673340056393069</v>
       </c>
       <c r="D2" t="n">
-        <v>32.55573562052847</v>
+        <v>28.47264691856599</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.37112599440108</v>
+        <v>29.51133598965912</v>
       </c>
       <c r="C3" t="n">
-        <v>42.36241343824987</v>
+        <v>49.29846096875358</v>
       </c>
       <c r="D3" t="n">
-        <v>118.2711459306132</v>
+        <v>113.4065860560703</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.28218786394211</v>
+        <v>28.37152690502857</v>
       </c>
       <c r="C4" t="n">
-        <v>80.66039138091794</v>
+        <v>105.4200684820225</v>
       </c>
       <c r="D4" t="n">
-        <v>132.8216286552552</v>
+        <v>133.4852901033261</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.84637399871455</v>
+        <v>37.69911184307752</v>
       </c>
       <c r="C5" t="n">
-        <v>68.37872760079036</v>
+        <v>110.2993545721292</v>
       </c>
       <c r="D5" t="n">
-        <v>70.93127163183206</v>
+        <v>74.73554398578845</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.34724525432967</v>
+        <v>35.38120551335081</v>
       </c>
       <c r="C6" t="n">
-        <v>83.03916606830798</v>
+        <v>108.4782125807513</v>
       </c>
       <c r="D6" t="n">
-        <v>31.55729820530948</v>
+        <v>33.24786775202249</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.63146906247572</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="C7" t="n">
-        <v>81.50567615427445</v>
+        <v>77.19384023722245</v>
       </c>
       <c r="D7" t="n">
-        <v>28.7455727803466</v>
+        <v>28.26647990067416</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.85246010692249</v>
+        <v>12.60073178400781</v>
       </c>
       <c r="C8" t="n">
-        <v>60.8339964936536</v>
+        <v>44.6449768506237</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>39.2718716652809</v>
+        <v>29.17656002251095</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1971,7 +1971,7 @@
         <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.219952543480291</v>
+        <v>5.43593703841459</v>
       </c>
       <c r="C2" t="n">
-        <v>3.065016332658542</v>
+        <v>4.347178834404876</v>
       </c>
       <c r="D2" t="n">
-        <v>22.93068112809275</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.70630287217674</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="C3" t="n">
-        <v>33.55122779263475</v>
+        <v>40.42837046088366</v>
       </c>
       <c r="D3" t="n">
-        <v>117.510291459822</v>
+        <v>111.8996033300514</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.68380479043707</v>
+        <v>39.93455136564751</v>
       </c>
       <c r="C4" t="n">
-        <v>95.93736740670256</v>
+        <v>116.5236350170539</v>
       </c>
       <c r="D4" t="n">
-        <v>158.1556281633441</v>
+        <v>153.9439305121253</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.65064635267094</v>
+        <v>41.45429681182157</v>
       </c>
       <c r="C5" t="n">
-        <v>106.0287520586555</v>
+        <v>150.5510104462484</v>
       </c>
       <c r="D5" t="n">
-        <v>93.14331344041615</v>
+        <v>97.31574118346511</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.35103337642641</v>
+        <v>41.90197376495812</v>
       </c>
       <c r="C6" t="n">
-        <v>97.32850390362032</v>
+        <v>138.3449412393478</v>
       </c>
       <c r="D6" t="n">
-        <v>40.21140421824511</v>
+        <v>41.53970886209105</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.07441720354028</v>
+        <v>22.45747873464579</v>
       </c>
       <c r="C7" t="n">
-        <v>100.1902984614997</v>
+        <v>106.2388460673643</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.43245201595411</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>78.10784734987622</v>
+        <v>61.00089360337556</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>45.15155866601504</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
         <v>30.03657101143117</v>
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2268,7 +2268,7 @@
         <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.76187727622453</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C2" t="n">
-        <v>6.451064164605791</v>
+        <v>12.00186568441726</v>
       </c>
       <c r="D2" t="n">
-        <v>23.86137795171873</v>
+        <v>24.66542932149686</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.15942834318226</v>
+        <v>24.65659359215864</v>
       </c>
       <c r="C3" t="n">
-        <v>22.15313694632928</v>
+        <v>28.2694251437869</v>
       </c>
       <c r="D3" t="n">
-        <v>110.1422749394497</v>
+        <v>102.7349885109075</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.8008948091497</v>
+        <v>48.0005905037393</v>
       </c>
       <c r="C4" t="n">
-        <v>89.67087181049517</v>
+        <v>108.6107485208246</v>
       </c>
       <c r="D4" t="n">
-        <v>177.3890474372434</v>
+        <v>171.6202979270892</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.33282213840224</v>
+        <v>49.75006491270713</v>
       </c>
       <c r="C5" t="n">
-        <v>140.7335334037803</v>
+        <v>182.7277914529376</v>
       </c>
       <c r="D5" t="n">
-        <v>122.7184630308513</v>
+        <v>124.8783079801943</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.54978838104078</v>
+        <v>48.30198704894308</v>
       </c>
       <c r="C6" t="n">
-        <v>131.8644246436146</v>
+        <v>183.9098156888508</v>
       </c>
       <c r="D6" t="n">
-        <v>55.8692983532775</v>
+        <v>57.9623844587317</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.45287309576081</v>
+        <v>33.35684174719388</v>
       </c>
       <c r="C7" t="n">
-        <v>119.3540136483975</v>
+        <v>149.1775454080071</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.85660808191773</v>
+        <v>15.35453409442011</v>
       </c>
       <c r="C8" t="n">
-        <v>104.1437964665016</v>
+        <v>95.63204387068178</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>68.33749419721195</v>
+        <v>51.25312064790897</v>
       </c>
       <c r="D9" t="n">
         <v>29.28749751309084</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>41.42484438069417</v>
+        <v>35.16129402759952</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2523,7 +2523,7 @@
         <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>14.05273663858884</v>
+      </c>
+      <c r="D16" t="n">
         <v>14.46605242207675</v>
-      </c>
-      <c r="D16" t="n">
-        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.442989198793564</v>
+        <v>3.45967890976576</v>
       </c>
       <c r="C2" t="n">
-        <v>3.017892442854695</v>
+        <v>5.779548734900973</v>
       </c>
       <c r="D2" t="n">
-        <v>16.64749582091316</v>
+        <v>17.21200075085508</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.65030219530566</v>
+        <v>24.61241494546753</v>
       </c>
       <c r="C3" t="n">
-        <v>24.65659359215864</v>
+        <v>37.38495257771854</v>
       </c>
       <c r="D3" t="n">
-        <v>108.6254747363883</v>
+        <v>102.5730001397068</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.79111838983624</v>
+        <v>52.46754255806228</v>
       </c>
       <c r="C4" t="n">
-        <v>86.49295449184824</v>
+        <v>106.6963404975434</v>
       </c>
       <c r="D4" t="n">
-        <v>190.5346491971082</v>
+        <v>183.5023903915883</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.0817157102933</v>
+        <v>51.81173509162543</v>
       </c>
       <c r="C5" t="n">
-        <v>167.3388961888689</v>
+        <v>216.1808444751477</v>
       </c>
       <c r="D5" t="n">
-        <v>130.1061145053086</v>
+        <v>131.9959788359837</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.14348370020284</v>
+        <v>39.88939097125216</v>
       </c>
       <c r="C6" t="n">
-        <v>161.2078817758475</v>
+        <v>212.5287430153495</v>
       </c>
       <c r="D6" t="n">
-        <v>54.46049039768332</v>
+        <v>56.27181491201868</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.13890945238431</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C7" t="n">
-        <v>129.2951909016007</v>
+        <v>143.5482040718558</v>
       </c>
       <c r="D7" t="n">
-        <v>34.85400699617026</v>
+        <v>34.6743471662931</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>83.03131208667398</v>
+        <v>65.84090978531233</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>31.61718481526852</v>
+        <v>26.84687272033327</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>19.90198946049134</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2820,7 +2820,7 @@
         <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>11.82515109765283</v>
+      </c>
+      <c r="D15" t="n">
         <v>12.18348900970292</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.820962064928586</v>
+        <v>4.526838664282042</v>
       </c>
       <c r="C2" t="n">
-        <v>4.28140173822034</v>
+        <v>6.783876636345459</v>
       </c>
       <c r="D2" t="n">
-        <v>17.86289947877071</v>
+        <v>17.92474958413826</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.93653055658923</v>
+        <v>18.39795197758523</v>
       </c>
       <c r="C3" t="n">
-        <v>17.86780821729195</v>
+        <v>30.11511082777091</v>
       </c>
       <c r="D3" t="n">
-        <v>97.87042863636452</v>
+        <v>93.72745332444299</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.66425195181014</v>
+        <v>50.22130381074558</v>
       </c>
       <c r="C4" t="n">
-        <v>74.7767773893668</v>
+        <v>100.187353218387</v>
       </c>
       <c r="D4" t="n">
-        <v>201.5616394112084</v>
+        <v>190.7005645591259</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.24909584610077</v>
+        <v>62.73367830137119</v>
       </c>
       <c r="C5" t="n">
-        <v>165.0072453912827</v>
+        <v>208.9895425415398</v>
       </c>
       <c r="D5" t="n">
-        <v>160.1721379478671</v>
+        <v>159.7794388661684</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.65545728020094</v>
+        <v>50.79758971313847</v>
       </c>
       <c r="C6" t="n">
-        <v>209.1073522660494</v>
+        <v>269.9678559477177</v>
       </c>
       <c r="D6" t="n">
-        <v>75.10958986110649</v>
+        <v>77.60519252530189</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.65521093382689</v>
+        <v>21.73883941513712</v>
       </c>
       <c r="C7" t="n">
-        <v>176.1864064995411</v>
+        <v>212.2381456948924</v>
       </c>
       <c r="D7" t="n">
-        <v>40.66300816219864</v>
+        <v>40.06414206260808</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.009678608322226</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>119.8321247803657</v>
+        <v>113.0727918366264</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>33.04562772494764</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>57.90937008270233</v>
+        <v>46.03905859065416</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>28.18597658892593</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.991385254840031</v>
+        <v>3.129811681138832</v>
       </c>
       <c r="C2" t="n">
-        <v>2.967823309938108</v>
+        <v>3.623630776374977</v>
       </c>
       <c r="D2" t="n">
-        <v>13.07197068204628</v>
+        <v>14.57208117413541</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.04666622591412</v>
+        <v>17.25912464065892</v>
       </c>
       <c r="C3" t="n">
-        <v>17.48001787411446</v>
+        <v>29.01064466049325</v>
       </c>
       <c r="D3" t="n">
-        <v>91.51852098988766</v>
+        <v>88.31802347404306</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.83994373314132</v>
+        <v>45.20555478974863</v>
       </c>
       <c r="C4" t="n">
-        <v>63.67321085433538</v>
+        <v>92.58077200588271</v>
       </c>
       <c r="D4" t="n">
-        <v>204.4715396065959</v>
+        <v>193.3424476312541</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.1641257641878</v>
+        <v>68.86960145291376</v>
       </c>
       <c r="C5" t="n">
-        <v>160.1721379478671</v>
+        <v>205.1607264949772</v>
       </c>
       <c r="D5" t="n">
-        <v>184.5685683984004</v>
+        <v>179.8316357254095</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.71207985187777</v>
+        <v>58.72716592033996</v>
       </c>
       <c r="C6" t="n">
-        <v>236.8004915074434</v>
+        <v>302.4106905822578</v>
       </c>
       <c r="D6" t="n">
-        <v>91.8542787047401</v>
+        <v>92.33729857522952</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.0382724649324</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="C7" t="n">
-        <v>221.2211371887508</v>
+        <v>269.3699715958313</v>
       </c>
       <c r="D7" t="n">
-        <v>46.71155576806323</v>
+        <v>45.21439051908685</v>
       </c>
     </row>
     <row r="8">
@@ -3352,10 +3352,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>151.7094727372596</v>
+        <v>150.04050164004</v>
       </c>
       <c r="D8" t="n">
         <v>34.29735604786232</v>
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>67.44999427257284</v>
+        <v>51.9187455913883</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
         <v>25.33890824661018</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3428,7 +3428,7 @@
         <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.389794896314989</v>
+        <v>5.450663253978291</v>
       </c>
       <c r="C2" t="n">
-        <v>4.106650646864408</v>
+        <v>5.17086515826795</v>
       </c>
       <c r="D2" t="n">
-        <v>19.53972455762426</v>
+        <v>20.6981868486355</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.17505419099219</v>
+        <v>14.08317081742049</v>
       </c>
       <c r="C3" t="n">
-        <v>14.73603304074462</v>
+        <v>22.23658550119026</v>
       </c>
       <c r="D3" t="n">
-        <v>82.52080328046566</v>
+        <v>81.0727254167016</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.44582093538184</v>
+        <v>39.1815508764902</v>
       </c>
       <c r="C4" t="n">
-        <v>54.03735713715294</v>
+        <v>83.73620693832321</v>
       </c>
       <c r="D4" t="n">
-        <v>203.067640389523</v>
+        <v>192.3341927389926</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.50144606382121</v>
+        <v>68.86960145291376</v>
       </c>
       <c r="C5" t="n">
-        <v>141.2489509485099</v>
+        <v>190.4590546238812</v>
       </c>
       <c r="D5" t="n">
-        <v>206.9769597478339</v>
+        <v>196.5949777754238</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>73.62027859376408</v>
+        <v>69.87687459747099</v>
       </c>
       <c r="C6" t="n">
-        <v>247.2659220347145</v>
+        <v>312.3931012390394</v>
       </c>
       <c r="D6" t="n">
-        <v>116.0857755409599</v>
+        <v>116.4077887879528</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.24380189248525</v>
+        <v>35.45287309576081</v>
       </c>
       <c r="C7" t="n">
-        <v>269.9089510854628</v>
+        <v>332.9096647623892</v>
       </c>
       <c r="D7" t="n">
-        <v>57.67080539057038</v>
+        <v>55.57477404200344</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>206.8689675003666</v>
+        <v>226.4793778926967</v>
       </c>
       <c r="D8" t="n">
-        <v>37.55184968744049</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>112.7124904291678</v>
+        <v>96.62655429508378</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>48.54251523648354</v>
+        <v>40.42837046088366</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.970809610779853</v>
+        <v>7.111780369563895</v>
       </c>
       <c r="C2" t="n">
-        <v>5.469316460358981</v>
+        <v>2.592795686915826</v>
       </c>
       <c r="D2" t="n">
-        <v>7.065638227464294</v>
+        <v>7.748934629620075</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.855323234577225</v>
+        <v>3.981968688425063</v>
       </c>
       <c r="C2" t="n">
-        <v>2.331650797586175</v>
+        <v>3.061089341841555</v>
       </c>
       <c r="D2" t="n">
-        <v>14.38162211951153</v>
+        <v>15.39969448881547</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.13288009743859</v>
+        <v>18.96736564604837</v>
       </c>
       <c r="C3" t="n">
-        <v>17.35239067256238</v>
+        <v>25.32418203104648</v>
       </c>
       <c r="D3" t="n">
-        <v>90.71839661092652</v>
+        <v>89.30467991681111</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.02084735262999</v>
+        <v>53.11844128597792</v>
       </c>
       <c r="C4" t="n">
-        <v>78.47796623437728</v>
+        <v>117.2893982263664</v>
       </c>
       <c r="D4" t="n">
-        <v>206.0924050663074</v>
+        <v>194.4017534041364</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.36870483510285</v>
+        <v>39.98167525545136</v>
       </c>
       <c r="C5" t="n">
-        <v>210.3885330200915</v>
+        <v>271.8950266911542</v>
       </c>
       <c r="D5" t="n">
-        <v>185.673034565678</v>
+        <v>177.0091110756999</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.95602664195392</v>
+        <v>22.01765576314322</v>
       </c>
       <c r="C6" t="n">
-        <v>226.2143060125501</v>
+        <v>274.3552864379967</v>
       </c>
       <c r="D6" t="n">
-        <v>89.92219922278237</v>
+        <v>88.110874708447</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.366053024963818</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>145.4645755905456</v>
+        <v>159.2384958811284</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>32.5184292077671</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>83.03131208667398</v>
+        <v>71.18161729641498</v>
       </c>
       <c r="D8" t="n">
-        <v>24.86766934857171</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>37.05312185368311</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>20.4988920646734</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.978663592413827</v>
+        <v>7.486807992586176</v>
       </c>
       <c r="C2" t="n">
-        <v>6.53451271946677</v>
+        <v>3.282964323001334</v>
       </c>
       <c r="D2" t="n">
-        <v>14.2805021059741</v>
+        <v>27.48206348498096</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.92533042121501</v>
+        <v>15.10418842983718</v>
       </c>
       <c r="C3" t="n">
-        <v>13.77882902910398</v>
+        <v>6.636614480708438</v>
       </c>
       <c r="D3" t="n">
-        <v>9.071348787240529</v>
+        <v>9.645671194224912</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39848186596707</v>
+        <v>13.3990067845556</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14499329829819</v>
+        <v>70.14774140149699</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57629198423142</v>
+        <v>1.576353739359483</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.984734005088556</v>
+        <v>6.812347319768617</v>
       </c>
       <c r="C2" t="n">
-        <v>4.80761850769663</v>
+        <v>8.164213908516475</v>
       </c>
       <c r="D2" t="n">
-        <v>26.23229865747477</v>
+        <v>27.59005573244811</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.34105166846792</v>
+        <v>21.57390580082366</v>
       </c>
       <c r="C3" t="n">
-        <v>21.10266690278519</v>
+        <v>10.4948829583984</v>
       </c>
       <c r="D3" t="n">
-        <v>18.87409961414493</v>
+        <v>30.39981766200248</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.53972455762427</v>
+        <v>17.4976893327909</v>
       </c>
       <c r="C4" t="n">
-        <v>21.5307089018368</v>
+        <v>10.66963404975434</v>
       </c>
       <c r="D4" t="n">
-        <v>19.82050440103886</v>
+        <v>20.12680968476386</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44170649367151</v>
+        <v>15.44210388514801</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14846780679898</v>
+        <v>86.15068483293101</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250885577615056</v>
+        <v>3.250969238978529</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.510549863937347</v>
+        <v>6.521749999311561</v>
       </c>
       <c r="C2" t="n">
-        <v>2.978622534684823</v>
+        <v>8.765043503515523</v>
       </c>
       <c r="D2" t="n">
-        <v>29.89127235120263</v>
+        <v>24.59867047760808</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.8684301120977</v>
+        <v>22.72255061479242</v>
       </c>
       <c r="C3" t="n">
-        <v>19.64968030049991</v>
+        <v>23.39504779220149</v>
       </c>
       <c r="D3" t="n">
-        <v>35.48036203147973</v>
+        <v>45.41564879845745</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.15303913533804</v>
+        <v>31.16656261901924</v>
       </c>
       <c r="C4" t="n">
-        <v>39.96007680595792</v>
+        <v>19.85879256150448</v>
       </c>
       <c r="D4" t="n">
-        <v>24.8234907018806</v>
+        <v>30.82196917482861</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.56699250916493</v>
+        <v>15.2661768010379</v>
       </c>
       <c r="C5" t="n">
-        <v>24.98547907308133</v>
+        <v>13.54811831860599</v>
       </c>
       <c r="D5" t="n">
-        <v>29.57514959043517</v>
+        <v>29.67332436085985</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="D6" t="n">
         <v>36.6290068454485</v>
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.78845088416398</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5249,7 +5249,7 @@
         <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5319,7 +5319,7 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73403652899767</v>
+        <v>16.73603012077649</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0776228268858</v>
+        <v>102.0897837367366</v>
       </c>
       <c r="D21" t="n">
-        <v>4.183509132249417</v>
+        <v>5.020809036232946</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.388232311533995</v>
+        <v>5.929756133650734</v>
       </c>
       <c r="C2" t="n">
-        <v>3.950552761889165</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="D2" t="n">
-        <v>31.10962125217293</v>
+        <v>24.72924292227291</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.23382018452676</v>
+        <v>22.52129233542183</v>
       </c>
       <c r="C3" t="n">
-        <v>14.97165248976386</v>
+        <v>29.51133598965912</v>
       </c>
       <c r="D3" t="n">
-        <v>50.30475236560656</v>
+        <v>54.00594121061704</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.76038111136832</v>
+        <v>38.24987230515998</v>
       </c>
       <c r="C4" t="n">
-        <v>45.10345302850696</v>
+        <v>41.46607778427253</v>
       </c>
       <c r="D4" t="n">
-        <v>36.36098972218912</v>
+        <v>45.79263991688822</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.74757733348411</v>
+        <v>30.87596529856219</v>
       </c>
       <c r="C5" t="n">
-        <v>51.0999680060465</v>
+        <v>25.89359569950963</v>
       </c>
       <c r="D5" t="n">
-        <v>31.51410130632262</v>
+        <v>33.60031517784709</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.20883452356409</v>
+        <v>13.36354975020759</v>
       </c>
       <c r="C6" t="n">
-        <v>26.72709950041517</v>
+        <v>17.06670209062656</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
         <v>33.22921454564179</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05820607809142</v>
+        <v>18.06291741386821</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8082967951678</v>
+        <v>117.8390326523783</v>
       </c>
       <c r="D21" t="n">
-        <v>6.019402026030472</v>
+        <v>6.881111395759318</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.698464586075987</v>
+        <v>7.332673603019426</v>
       </c>
       <c r="C2" t="n">
-        <v>5.480115685105695</v>
+        <v>14.03113818909541</v>
       </c>
       <c r="D2" t="n">
-        <v>30.11903781858789</v>
+        <v>37.96712896633689</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.83482970597506</v>
+        <v>18.9280957378785</v>
       </c>
       <c r="C3" t="n">
-        <v>14.26479414270615</v>
+        <v>26.64463269325843</v>
       </c>
       <c r="D3" t="n">
-        <v>59.04230693340318</v>
+        <v>57.19171251089794</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.19284882285566</v>
+        <v>29.83923972287755</v>
       </c>
       <c r="C4" t="n">
-        <v>34.14027641518283</v>
+        <v>49.58316780298516</v>
       </c>
       <c r="D4" t="n">
-        <v>45.81816535719864</v>
+        <v>53.79486545420397</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.42159603794517</v>
+        <v>27.26804248545517</v>
       </c>
       <c r="C5" t="n">
-        <v>50.46183199828607</v>
+        <v>39.83441309981433</v>
       </c>
       <c r="D5" t="n">
-        <v>29.86967390170921</v>
+        <v>33.74757733348411</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.26166897314417</v>
+        <v>14.97361598517235</v>
       </c>
       <c r="C6" t="n">
-        <v>37.35353665118265</v>
+        <v>20.12582793705961</v>
       </c>
       <c r="D6" t="n">
-        <v>30.79251674370121</v>
+        <v>31.23528495831652</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.347980655659875</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>19.22360179685679</v>
+        <v>14.73210604992764</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5916,7 +5916,7 @@
         <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.057401886563224</v>
+        <v>7.060196626808141</v>
       </c>
       <c r="C21" t="n">
-        <v>66.16314268653022</v>
+        <v>66.18934337632632</v>
       </c>
       <c r="D21" t="n">
-        <v>4.410876179102015</v>
+        <v>5.295147470106106</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.096072406295946</v>
+        <v>6.787803627162447</v>
       </c>
       <c r="C2" t="n">
-        <v>8.050331174823844</v>
+        <v>6.185992284459152</v>
       </c>
       <c r="D2" t="n">
-        <v>37.18369429834794</v>
+        <v>32.40160123096173</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.74080291054562</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="C3" t="n">
-        <v>18.95754816900591</v>
+        <v>44.82169143738813</v>
       </c>
       <c r="D3" t="n">
-        <v>71.27979206683966</v>
+        <v>75.26568774608171</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.87225929192346</v>
+        <v>34.2551408965797</v>
       </c>
       <c r="C4" t="n">
-        <v>35.23787034853076</v>
+        <v>60.45700537522283</v>
       </c>
       <c r="D4" t="n">
-        <v>65.68972063885833</v>
+        <v>70.76928326063133</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.66827675361837</v>
+        <v>37.77274292089604</v>
       </c>
       <c r="C5" t="n">
-        <v>58.4385320952914</v>
+        <v>71.49577656177398</v>
       </c>
       <c r="D5" t="n">
-        <v>40.6934423410303</v>
+        <v>46.75573441475435</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.34345713223292</v>
+        <v>27.4113776502752</v>
       </c>
       <c r="C6" t="n">
-        <v>63.03409309887072</v>
+        <v>45.44411948188061</v>
       </c>
       <c r="D6" t="n">
-        <v>33.52962934314132</v>
+        <v>35.38120551335081</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.89369351050086</v>
+        <v>12.87562114119692</v>
       </c>
       <c r="C7" t="n">
-        <v>39.82459562277186</v>
+        <v>23.05634483423634</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>23.03180114163017</v>
+        <v>19.61041039233004</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
         <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6227,7 +6227,7 @@
         <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>19.66637001147211</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.280670187950782</v>
+        <v>7.281325811302288</v>
       </c>
       <c r="C21" t="n">
-        <v>75.53695319998937</v>
+        <v>75.54375529226125</v>
       </c>
       <c r="D21" t="n">
-        <v>5.460502640963086</v>
+        <v>6.371160084889502</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.832563110930301</v>
+        <v>6.127087422204344</v>
       </c>
       <c r="C2" t="n">
-        <v>5.937610115284709</v>
+        <v>4.636794407157685</v>
       </c>
       <c r="D2" t="n">
-        <v>32.64114767079795</v>
+        <v>36.41793108903543</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.35086914551039</v>
+        <v>23.41959148480766</v>
       </c>
       <c r="C3" t="n">
-        <v>26.45810062945154</v>
+        <v>32.42221793275092</v>
       </c>
       <c r="D3" t="n">
-        <v>84.48920742748049</v>
+        <v>83.72344421816798</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.59446574935061</v>
+        <v>40.73860273542564</v>
       </c>
       <c r="C4" t="n">
-        <v>42.4615699563788</v>
+        <v>89.83678717251287</v>
       </c>
       <c r="D4" t="n">
-        <v>86.65886985386595</v>
+        <v>92.59353472603793</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.91495746929158</v>
+        <v>45.20948178056562</v>
       </c>
       <c r="C5" t="n">
-        <v>61.75193059712439</v>
+        <v>94.49321653375551</v>
       </c>
       <c r="D5" t="n">
-        <v>54.68334712654735</v>
+        <v>61.1628819745763</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.45291415348983</v>
+        <v>40.49316580936395</v>
       </c>
       <c r="C6" t="n">
-        <v>79.89953691012668</v>
+        <v>82.83790778893737</v>
       </c>
       <c r="D6" t="n">
-        <v>39.08435785376978</v>
+        <v>42.38499363544755</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.45180923259856</v>
+        <v>23.35577788403162</v>
       </c>
       <c r="C7" t="n">
-        <v>68.33062196328224</v>
+        <v>46.17257627843174</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>39.55461500410399</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>26.62499773917349</v>
+        <v>24.62812290873548</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
         <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6633,7 +6633,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.491195859964595</v>
+        <v>7.488644421333814</v>
       </c>
       <c r="C21" t="n">
-        <v>84.2759534246017</v>
+        <v>85.18333029267214</v>
       </c>
       <c r="D21" t="n">
-        <v>6.554796377469021</v>
+        <v>7.488644421333814</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_43_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_43_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497615976542</v>
+        <v>10.84497636160854</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907134101269</v>
+        <v>37.78907204433041</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.722026530977911</v>
+        <v>5.508586368528853</v>
       </c>
       <c r="C2" t="n">
-        <v>7.046003273379358</v>
+        <v>4.396266219617217</v>
       </c>
       <c r="D2" t="n">
-        <v>41.05178025308038</v>
+        <v>23.43431770037136</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.20222433154161</v>
+        <v>18.6532063806894</v>
       </c>
       <c r="C3" t="n">
-        <v>24.45533531278805</v>
+        <v>14.34824269756713</v>
       </c>
       <c r="D3" t="n">
-        <v>92.12720456652069</v>
+        <v>77.73478322226245</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.60195987808609</v>
+        <v>34.75288698263284</v>
       </c>
       <c r="C4" t="n">
-        <v>84.28500390499717</v>
+        <v>39.06668639509333</v>
       </c>
       <c r="D4" t="n">
-        <v>110.4996311037955</v>
+        <v>101.8847949990297</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.91620125890309</v>
+        <v>43.6632291463769</v>
       </c>
       <c r="C5" t="n">
-        <v>131.5787360616788</v>
+        <v>74.39193228930206</v>
       </c>
       <c r="D5" t="n">
-        <v>79.49702035138549</v>
+        <v>72.57569903644547</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.20010627187966</v>
+        <v>42.38499363544755</v>
       </c>
       <c r="C6" t="n">
-        <v>115.7637622939669</v>
+        <v>91.25050386662829</v>
       </c>
       <c r="D6" t="n">
-        <v>51.24035792775378</v>
+        <v>47.81896717845365</v>
       </c>
     </row>
     <row r="7">
@@ -850,10 +850,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.39298648580176</v>
+        <v>30.72183090899544</v>
       </c>
       <c r="C7" t="n">
-        <v>83.12261462316894</v>
+        <v>77.49327328701773</v>
       </c>
       <c r="D7" t="n">
         <v>39.58504918293564</v>
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.7745421853885</v>
+        <v>16.10557108816892</v>
       </c>
       <c r="C8" t="n">
-        <v>43.39324852770901</v>
+        <v>48.81740459367264</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.209374302911826</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>28.51093507903161</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
         <v>34.05780960802609</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.679908126032064</v>
+        <v>7.716697278998705</v>
       </c>
       <c r="C21" t="n">
-        <v>94.07887454389278</v>
+        <v>96.45871598748383</v>
       </c>
       <c r="D21" t="n">
-        <v>8.639896641786072</v>
+        <v>8.681284438873544</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.185231520933158</v>
+        <v>6.658212930201868</v>
       </c>
       <c r="C2" t="n">
-        <v>11.36078443354409</v>
+        <v>8.497026380256143</v>
       </c>
       <c r="D2" t="n">
-        <v>37.81986681069987</v>
+        <v>25.12685074249287</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.36912144126357</v>
+        <v>18.59430151843459</v>
       </c>
       <c r="C3" t="n">
-        <v>25.78069471352124</v>
+        <v>15.79141182280995</v>
       </c>
       <c r="D3" t="n">
-        <v>102.2048447506142</v>
+        <v>78.06366870318513</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.81067122846316</v>
+        <v>35.35273482992764</v>
       </c>
       <c r="C4" t="n">
-        <v>72.78579304515428</v>
+        <v>37.35648189429538</v>
       </c>
       <c r="D4" t="n">
-        <v>125.891471610977</v>
+        <v>116.102465251932</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.5304154688631</v>
+        <v>47.71293842639499</v>
       </c>
       <c r="C5" t="n">
-        <v>141.3225820263284</v>
+        <v>73.18929135159972</v>
       </c>
       <c r="D5" t="n">
-        <v>97.4875470317083</v>
+        <v>89.78082755337083</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.25672884355649</v>
+        <v>50.59633143376788</v>
       </c>
       <c r="C6" t="n">
-        <v>158.7927824234004</v>
+        <v>103.8895238111017</v>
       </c>
       <c r="D6" t="n">
-        <v>61.42402686390595</v>
+        <v>58.76741757621409</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.25053525769474</v>
+        <v>40.90255460203486</v>
       </c>
       <c r="C7" t="n">
-        <v>120.6715190674967</v>
+        <v>104.8614540383061</v>
       </c>
       <c r="D7" t="n">
-        <v>44.55563780953724</v>
+        <v>43.71722527011047</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.78698611037422</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="C8" t="n">
-        <v>73.8519710519663</v>
+        <v>74.93680226515903</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.42499894494763</v>
+        <v>11.98124898262807</v>
       </c>
       <c r="C9" t="n">
-        <v>39.93749660876023</v>
+        <v>46.26093357181394</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.854477833619981</v>
+        <v>7.908697058462047</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1082118370598</v>
+        <v>105.7788231569299</v>
       </c>
       <c r="D21" t="n">
-        <v>9.818097292024976</v>
+        <v>9.885871323077559</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.356055621472102</v>
+        <v>8.506843857298612</v>
       </c>
       <c r="C2" t="n">
-        <v>11.02600846639593</v>
+        <v>9.322676199527711</v>
       </c>
       <c r="D2" t="n">
-        <v>34.3179727496515</v>
+        <v>23.23109592559227</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.59907138823558</v>
+        <v>20.26327261565417</v>
       </c>
       <c r="C3" t="n">
-        <v>33.85066084243002</v>
+        <v>24.38170423496954</v>
       </c>
       <c r="D3" t="n">
-        <v>106.0876569209103</v>
+        <v>79.28594459497242</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.47884050442774</v>
+        <v>35.25063306868597</v>
       </c>
       <c r="C4" t="n">
-        <v>68.14016290865837</v>
+        <v>38.31368590593603</v>
       </c>
       <c r="D4" t="n">
-        <v>140.9897695545887</v>
+        <v>126.746573861376</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.05212441044566</v>
+        <v>49.92187076095032</v>
       </c>
       <c r="C5" t="n">
-        <v>137.812833983646</v>
+        <v>70.34222300928397</v>
       </c>
       <c r="D5" t="n">
-        <v>115.3308115563941</v>
+        <v>106.6914317590221</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.93850371866029</v>
+        <v>56.91584140600459</v>
       </c>
       <c r="C6" t="n">
-        <v>184.5940938387108</v>
+        <v>110.0077755039679</v>
       </c>
       <c r="D6" t="n">
-        <v>73.21776203502289</v>
+        <v>71.56744414418399</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>57.01205268102077</v>
+        <v>50.2448657556475</v>
       </c>
       <c r="C7" t="n">
-        <v>164.7480639973615</v>
+        <v>125.2229014243849</v>
       </c>
       <c r="D7" t="n">
-        <v>50.48441219548373</v>
+        <v>49.22679338634357</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>36.46701847424777</v>
+        <v>33.21252483466959</v>
       </c>
       <c r="C8" t="n">
-        <v>109.8182981970482</v>
+        <v>104.8948334602505</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>41.80772598535042</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.19374845510188</v>
+        <v>17.52812351162255</v>
       </c>
       <c r="C9" t="n">
-        <v>60.57186985661969</v>
+        <v>67.22811929141305</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.683558444063038</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>38.29306920414684</v>
+        <v>43.70249905454677</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>37.15424186722054</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
-        <v>34.29539255245382</v>
+        <v>35.7169632282032</v>
       </c>
       <c r="D11" t="n">
         <v>36.96083756948391</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>31.73990327829938</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.012414965391846</v>
+        <v>8.087136003923183</v>
       </c>
       <c r="C21" t="n">
-        <v>109.1691539034639</v>
+        <v>114.2307960554149</v>
       </c>
       <c r="D21" t="n">
-        <v>11.01707057741379</v>
+        <v>11.11981200539437</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.672759219316323</v>
+        <v>7.609526455617027</v>
       </c>
       <c r="C2" t="n">
-        <v>7.673340056393069</v>
+        <v>6.115306449753382</v>
       </c>
       <c r="D2" t="n">
-        <v>28.47264691856599</v>
+        <v>18.85544640776424</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.51133598965912</v>
+        <v>24.84312565596554</v>
       </c>
       <c r="C3" t="n">
-        <v>49.29846096875358</v>
+        <v>35.63253292563798</v>
       </c>
       <c r="D3" t="n">
-        <v>113.4065860560703</v>
+        <v>88.799079849124</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.37152690502857</v>
+        <v>23.98115117163684</v>
       </c>
       <c r="C4" t="n">
-        <v>105.4200684820225</v>
+        <v>57.54710517983528</v>
       </c>
       <c r="D4" t="n">
-        <v>133.4852901033261</v>
+        <v>122.9815714155894</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.69911184307752</v>
+        <v>32.05406254365837</v>
       </c>
       <c r="C5" t="n">
-        <v>110.2993545721292</v>
+        <v>65.72800879932397</v>
       </c>
       <c r="D5" t="n">
-        <v>74.73554398578845</v>
+        <v>72.45298057341462</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.38120551335081</v>
+        <v>31.19503330244241</v>
       </c>
       <c r="C6" t="n">
-        <v>108.4782125807513</v>
+        <v>82.47564288607032</v>
       </c>
       <c r="D6" t="n">
-        <v>33.24786775202249</v>
+        <v>32.40258297866598</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.13430381349934</v>
+        <v>21.97838585497334</v>
       </c>
       <c r="C7" t="n">
-        <v>77.19384023722245</v>
+        <v>73.72041685959724</v>
       </c>
       <c r="D7" t="n">
-        <v>28.26647990067416</v>
+        <v>29.34443887993716</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C8" t="n">
-        <v>44.6449768506237</v>
+        <v>49.48499303256047</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>29.17656002251095</v>
+        <v>33.28124717396686</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D10" t="n">
         <v>28.89774367450487</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.43593703841459</v>
+        <v>4.502294971675872</v>
       </c>
       <c r="C2" t="n">
-        <v>4.347178834404876</v>
+        <v>2.716495897650924</v>
       </c>
       <c r="D2" t="n">
-        <v>19.96089432274615</v>
+        <v>13.95063487734718</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.37527396939631</v>
+        <v>26.32556468937822</v>
       </c>
       <c r="C3" t="n">
-        <v>40.42837046088366</v>
+        <v>29.96784867213389</v>
       </c>
       <c r="D3" t="n">
-        <v>111.8996033300514</v>
+        <v>85.18133955897451</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.93455136564751</v>
+        <v>34.71459882216722</v>
       </c>
       <c r="C4" t="n">
-        <v>116.5236350170539</v>
+        <v>75.73398140100744</v>
       </c>
       <c r="D4" t="n">
-        <v>153.9439305121253</v>
+        <v>136.9950381460084</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.45429681182157</v>
+        <v>35.76016012719008</v>
       </c>
       <c r="C5" t="n">
-        <v>150.5510104462484</v>
+        <v>86.9092155184489</v>
       </c>
       <c r="D5" t="n">
-        <v>97.31574118346511</v>
+        <v>93.6832746777519</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.90197376495812</v>
+        <v>37.0315234041897</v>
       </c>
       <c r="C6" t="n">
-        <v>138.3449412393478</v>
+        <v>95.87944429215202</v>
       </c>
       <c r="D6" t="n">
-        <v>41.53970886209105</v>
+        <v>42.0629803884546</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.45747873464579</v>
+        <v>21.43940636534185</v>
       </c>
       <c r="C7" t="n">
-        <v>106.2388460673643</v>
+        <v>94.56095712534852</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>32.33876937788993</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>61.00089360337556</v>
+        <v>65.92435834017331</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>28.53940576245478</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>40.38124657107979</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.674501730546564</v>
+        <v>4.490513999224911</v>
       </c>
       <c r="C2" t="n">
-        <v>12.00186568441726</v>
+        <v>5.537057051952011</v>
       </c>
       <c r="D2" t="n">
-        <v>24.66542932149686</v>
+        <v>18.39697022988098</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.65659359215864</v>
+        <v>20.66088043587412</v>
       </c>
       <c r="C3" t="n">
-        <v>28.2694251437869</v>
+        <v>19.20789383358884</v>
       </c>
       <c r="D3" t="n">
-        <v>102.7349885109075</v>
+        <v>77.65624340592271</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.0005905037393</v>
+        <v>43.09970596413923</v>
       </c>
       <c r="C4" t="n">
-        <v>108.6107485208246</v>
+        <v>75.28728619557515</v>
       </c>
       <c r="D4" t="n">
-        <v>171.6202979270892</v>
+        <v>147.4221805128138</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.75006491270713</v>
+        <v>43.78594760940775</v>
       </c>
       <c r="C5" t="n">
-        <v>182.7277914529376</v>
+        <v>115.2326367859694</v>
       </c>
       <c r="D5" t="n">
-        <v>124.8783079801943</v>
+        <v>118.5214915951962</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.30198704894308</v>
+        <v>42.82776185006286</v>
       </c>
       <c r="C6" t="n">
-        <v>183.9098156888508</v>
+        <v>116.810305346694</v>
       </c>
       <c r="D6" t="n">
-        <v>57.9623844587317</v>
+        <v>58.6064109527176</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.35684174719388</v>
+        <v>31.4404702285041</v>
       </c>
       <c r="C7" t="n">
-        <v>149.1775454080071</v>
+        <v>117.5574153496258</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.35453409442011</v>
+        <v>15.43798264928109</v>
       </c>
       <c r="C8" t="n">
-        <v>95.63204387068178</v>
+        <v>94.88100687693299</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>51.25312064790897</v>
+        <v>60.12811989430013</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>30.50780990946962</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>3.131775176547325</v>
       </c>
       <c r="C10" t="n">
-        <v>35.16129402759952</v>
+        <v>39.00483628972578</v>
       </c>
       <c r="D10" t="n">
         <v>30.32127784566274</v>
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.79680358741669</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>36.10868056219768</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.45967890976576</v>
+        <v>2.59770442543706</v>
       </c>
       <c r="C2" t="n">
-        <v>5.779548734900973</v>
+        <v>2.455351008321272</v>
       </c>
       <c r="D2" t="n">
-        <v>17.21200075085508</v>
+        <v>12.68516208657304</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.61241494546753</v>
+        <v>20.53325323432204</v>
       </c>
       <c r="C3" t="n">
-        <v>37.38495257771854</v>
+        <v>21.39719121405923</v>
       </c>
       <c r="D3" t="n">
-        <v>102.5730001397068</v>
+        <v>77.3960802642973</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.46754255806228</v>
+        <v>47.82191242156638</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6963404975434</v>
+        <v>72.41567416065323</v>
       </c>
       <c r="D4" t="n">
-        <v>183.5023903915883</v>
+        <v>155.2457279679566</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.81173509162543</v>
+        <v>46.19122948481243</v>
       </c>
       <c r="C5" t="n">
-        <v>216.1808444751477</v>
+        <v>136.8065425867931</v>
       </c>
       <c r="D5" t="n">
-        <v>131.9959788359837</v>
+        <v>128.1671627894211</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.88939097125216</v>
+        <v>37.71580155404972</v>
       </c>
       <c r="C6" t="n">
-        <v>212.5287430153495</v>
+        <v>150.9437095279471</v>
       </c>
       <c r="D6" t="n">
-        <v>56.27181491201868</v>
+        <v>57.43911293236815</v>
       </c>
     </row>
     <row r="7">
@@ -2719,10 +2719,10 @@
         <v>10.18072369303942</v>
       </c>
       <c r="C7" t="n">
-        <v>143.5482040718558</v>
+        <v>125.8217675239755</v>
       </c>
       <c r="D7" t="n">
-        <v>34.6743471662931</v>
+        <v>36.29128563518759</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>65.84090978531233</v>
+        <v>75.93818492349078</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>26.84687272033327</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.19655482949439</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.91537407545231</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.74977750860408</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.526838664282042</v>
+        <v>4.246058820867455</v>
       </c>
       <c r="C2" t="n">
-        <v>6.783876636345459</v>
+        <v>1.88986433067511</v>
       </c>
       <c r="D2" t="n">
-        <v>17.92474958413826</v>
+        <v>17.33373746618168</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.39795197758523</v>
+        <v>14.71639808665969</v>
       </c>
       <c r="C3" t="n">
-        <v>30.11511082777091</v>
+        <v>15.06491852166731</v>
       </c>
       <c r="D3" t="n">
-        <v>93.72745332444299</v>
+        <v>70.05751617505238</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.22130381074558</v>
+        <v>44.36321525950487</v>
       </c>
       <c r="C4" t="n">
-        <v>100.187353218387</v>
+        <v>62.52456604036662</v>
       </c>
       <c r="D4" t="n">
-        <v>190.7005645591259</v>
+        <v>159.9551717052286</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.73367830137119</v>
+        <v>57.92311455056183</v>
       </c>
       <c r="C5" t="n">
-        <v>208.9895425415398</v>
+        <v>136.4383871977005</v>
       </c>
       <c r="D5" t="n">
-        <v>159.7794388661684</v>
+        <v>150.4282919832175</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.79758971313847</v>
+        <v>48.50324532831367</v>
       </c>
       <c r="C6" t="n">
-        <v>269.9678559477177</v>
+        <v>185.5198819238155</v>
       </c>
       <c r="D6" t="n">
-        <v>77.60519252530189</v>
+        <v>78.65173557802898</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.73883941513712</v>
+        <v>22.15804568485051</v>
       </c>
       <c r="C7" t="n">
-        <v>212.2381456948924</v>
+        <v>168.580807034741</v>
       </c>
       <c r="D7" t="n">
-        <v>40.06414206260808</v>
+        <v>42.99858595060179</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>113.0727918366264</v>
+        <v>117.0783224699534</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>46.03905859065416</v>
+        <v>54.91405783704532</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>28.18597658892593</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>25.58827216348886</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>22.34752299177014</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.129811681138832</v>
+        <v>3.029673415305656</v>
       </c>
       <c r="C2" t="n">
-        <v>3.623630776374977</v>
+        <v>2.310052348092745</v>
       </c>
       <c r="D2" t="n">
-        <v>14.57208117413541</v>
+        <v>12.60073178400781</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.25912464065892</v>
+        <v>14.85384276525424</v>
       </c>
       <c r="C3" t="n">
-        <v>29.01064466049325</v>
+        <v>11.43736075447534</v>
       </c>
       <c r="D3" t="n">
-        <v>88.31802347404306</v>
+        <v>68.25600913775949</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.20555478974863</v>
+        <v>39.10497455555895</v>
       </c>
       <c r="C4" t="n">
-        <v>92.58077200588271</v>
+        <v>52.71003424101125</v>
       </c>
       <c r="D4" t="n">
-        <v>193.3424476312541</v>
+        <v>159.8147817835213</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.86960145291376</v>
+        <v>63.64179492779949</v>
       </c>
       <c r="C5" t="n">
-        <v>205.1607264949772</v>
+        <v>132.4623089955009</v>
       </c>
       <c r="D5" t="n">
-        <v>179.8316357254095</v>
+        <v>168.3451875857218</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.72716592033996</v>
+        <v>57.43911293236815</v>
       </c>
       <c r="C6" t="n">
-        <v>302.4106905822578</v>
+        <v>206.0482264196164</v>
       </c>
       <c r="D6" t="n">
-        <v>92.33729857522952</v>
+        <v>95.35617276578846</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.22360179685679</v>
+        <v>22.27781890476862</v>
       </c>
       <c r="C7" t="n">
-        <v>269.3699715958313</v>
+        <v>209.5432482467349</v>
       </c>
       <c r="D7" t="n">
-        <v>45.21439051908685</v>
+        <v>49.76577287597506</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
         <v>150.04050164004</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>51.9187455913883</v>
+        <v>69.33593161243097</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>25.23287949455151</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.450663253978291</v>
+        <v>4.245077073163208</v>
       </c>
       <c r="C2" t="n">
-        <v>5.17086515826795</v>
+        <v>5.648976290236146</v>
       </c>
       <c r="D2" t="n">
-        <v>20.6981868486355</v>
+        <v>14.88133170097315</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.08317081742049</v>
+        <v>12.56637061435917</v>
       </c>
       <c r="C3" t="n">
-        <v>22.23658550119026</v>
+        <v>10.14145378486955</v>
       </c>
       <c r="D3" t="n">
-        <v>81.0727254167016</v>
+        <v>63.10183369046374</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.1815508764902</v>
+        <v>34.15303913533804</v>
       </c>
       <c r="C4" t="n">
-        <v>83.73620693832321</v>
+        <v>41.01938257884023</v>
       </c>
       <c r="D4" t="n">
-        <v>192.3341927389926</v>
+        <v>157.657882077291</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.86960145291376</v>
+        <v>61.87464906015524</v>
       </c>
       <c r="C5" t="n">
-        <v>190.4590546238812</v>
+        <v>117.2452195796754</v>
       </c>
       <c r="D5" t="n">
-        <v>196.5949777754238</v>
+        <v>183.218665305061</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69.87687459747099</v>
+        <v>69.39385472698156</v>
       </c>
       <c r="C6" t="n">
-        <v>312.3931012390394</v>
+        <v>208.7853390190565</v>
       </c>
       <c r="D6" t="n">
-        <v>116.4077887879528</v>
+        <v>117.4543318406799</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.45287309576081</v>
+        <v>39.28561613314036</v>
       </c>
       <c r="C7" t="n">
-        <v>332.9096647623892</v>
+        <v>248.4096581101619</v>
       </c>
       <c r="D7" t="n">
-        <v>55.57477404200344</v>
+        <v>61.86286808770426</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C8" t="n">
-        <v>226.4793778926967</v>
+        <v>205.700687732313</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>96.62655429508378</v>
+        <v>115.8187401654047</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>40.42837046088366</v>
+        <v>51.38958357879929</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>27.18950266911542</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>25.05518316008284</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.111780369563895</v>
+        <v>5.765804267041517</v>
       </c>
       <c r="C2" t="n">
-        <v>2.592795686915826</v>
+        <v>3.257438882690916</v>
       </c>
       <c r="D2" t="n">
-        <v>7.748934629620075</v>
+        <v>7.823547455142832</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.981968688425063</v>
+        <v>2.938370878810703</v>
       </c>
       <c r="C2" t="n">
-        <v>3.061089341841555</v>
+        <v>3.073852061996763</v>
       </c>
       <c r="D2" t="n">
-        <v>15.39969448881547</v>
+        <v>10.83358591636355</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.96736564604837</v>
+        <v>16.99896149903352</v>
       </c>
       <c r="C3" t="n">
-        <v>25.32418203104648</v>
+        <v>15.59997102048182</v>
       </c>
       <c r="D3" t="n">
-        <v>89.30467991681111</v>
+        <v>69.4242889058132</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.11844128597792</v>
+        <v>46.85194568977053</v>
       </c>
       <c r="C4" t="n">
-        <v>117.2893982263664</v>
+        <v>59.89544568839366</v>
       </c>
       <c r="D4" t="n">
-        <v>194.4017534041364</v>
+        <v>164.2179202370682</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.98167525545136</v>
+        <v>42.5096755938869</v>
       </c>
       <c r="C5" t="n">
-        <v>271.8950266911542</v>
+        <v>175.9782759862408</v>
       </c>
       <c r="D5" t="n">
-        <v>177.0091110756999</v>
+        <v>168.0506632744478</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.01765576314322</v>
+        <v>24.39250345971625</v>
       </c>
       <c r="C6" t="n">
-        <v>274.3552864379967</v>
+        <v>210.6771668451401</v>
       </c>
       <c r="D6" t="n">
-        <v>88.110874708447</v>
+        <v>93.7461065308237</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>159.2384958811284</v>
+        <v>144.6261630511189</v>
       </c>
       <c r="D7" t="n">
-        <v>32.5184292077671</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>71.18161729641498</v>
+        <v>85.36787162278139</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>25.45180923259856</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>30.84062238120929</v>
+        <v>39.160934174701</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.4988920646734</v>
+        <v>23.77302065833652</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>17.41424077792992</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>17.05884810899257</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.486807992586176</v>
+        <v>6.56494689829842</v>
       </c>
       <c r="C2" t="n">
-        <v>3.282964323001334</v>
+        <v>3.517602024316322</v>
       </c>
       <c r="D2" t="n">
-        <v>27.48206348498096</v>
+        <v>17.84424627239003</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.10418842983718</v>
+        <v>12.24730261047896</v>
       </c>
       <c r="C3" t="n">
-        <v>6.636614480708438</v>
+        <v>8.33503800905542</v>
       </c>
       <c r="D3" t="n">
-        <v>9.645671194224912</v>
+        <v>10.0187353218387</v>
       </c>
     </row>
     <row r="4">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3990067845556</v>
+        <v>13.39911120893886</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14774140149699</v>
+        <v>70.14828809385637</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576353739359483</v>
+        <v>1.576366024581042</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.812347319768617</v>
+        <v>4.903829782712818</v>
       </c>
       <c r="C2" t="n">
-        <v>8.164213908516475</v>
+        <v>6.253732876052181</v>
       </c>
       <c r="D2" t="n">
-        <v>27.59005573244811</v>
+        <v>21.01038261858599</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.57390580082366</v>
+        <v>18.50103548653114</v>
       </c>
       <c r="C3" t="n">
-        <v>10.4948829583984</v>
+        <v>11.76133749687679</v>
       </c>
       <c r="D3" t="n">
-        <v>30.39981766200248</v>
+        <v>22.58510593619787</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.4976893327909</v>
+        <v>14.25595841336793</v>
       </c>
       <c r="C4" t="n">
-        <v>10.66963404975434</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D4" t="n">
-        <v>20.12680968476386</v>
+        <v>20.31825048709199</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
         <v>16.54343056426301</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44210388514801</v>
+        <v>15.44433458296807</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15068483293101</v>
+        <v>86.16312977866396</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250969238978529</v>
+        <v>3.251438859572225</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.521749999311561</v>
+        <v>5.017712516405448</v>
       </c>
       <c r="C2" t="n">
-        <v>8.765043503515523</v>
+        <v>4.580834788015617</v>
       </c>
       <c r="D2" t="n">
-        <v>24.59867047760808</v>
+        <v>23.49911304885165</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.72255061479242</v>
+        <v>17.64691498383642</v>
       </c>
       <c r="C3" t="n">
-        <v>23.39504779220149</v>
+        <v>19.38460842035327</v>
       </c>
       <c r="D3" t="n">
-        <v>45.41564879845745</v>
+        <v>34.1500938922253</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.16656261901924</v>
+        <v>26.39330528097125</v>
       </c>
       <c r="C4" t="n">
-        <v>19.85879256150448</v>
+        <v>22.74316731658161</v>
       </c>
       <c r="D4" t="n">
-        <v>30.82196917482861</v>
+        <v>27.0697294491973</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.2661768010379</v>
+        <v>12.73817646260237</v>
       </c>
       <c r="C5" t="n">
-        <v>13.54811831860599</v>
+        <v>16.66516727958961</v>
       </c>
       <c r="D5" t="n">
-        <v>29.67332436085985</v>
+        <v>29.74695543867836</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.07549676223577</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
         <v>36.6290068454485</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
         <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5361,7 +5361,7 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73603012077649</v>
+        <v>16.74233284203892</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0897837367366</v>
+        <v>102.1282303364374</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020809036232946</v>
+        <v>5.022699852611676</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.929756133650734</v>
+        <v>4.994150571503524</v>
       </c>
       <c r="C2" t="n">
-        <v>7.083309686140737</v>
+        <v>5.400594121061704</v>
       </c>
       <c r="D2" t="n">
-        <v>24.72924292227291</v>
+        <v>31.20681427489336</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.52129233542183</v>
+        <v>17.40147805777471</v>
       </c>
       <c r="C3" t="n">
-        <v>29.51133598965912</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D3" t="n">
-        <v>54.00594121061704</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.24987230515998</v>
+        <v>30.51566389110361</v>
       </c>
       <c r="C4" t="n">
-        <v>41.46607778427253</v>
+        <v>37.39477005476101</v>
       </c>
       <c r="D4" t="n">
-        <v>45.79263991688822</v>
+        <v>37.24161741289851</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.87596529856219</v>
+        <v>26.48264432205772</v>
       </c>
       <c r="C5" t="n">
-        <v>25.89359569950963</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D5" t="n">
-        <v>33.60031517784709</v>
+        <v>32.88854809226815</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.36354975020759</v>
+        <v>11.55222523587222</v>
       </c>
       <c r="C6" t="n">
-        <v>17.06670209062656</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
         <v>38.19882142453915</v>
@@ -5515,7 +5515,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
         <v>41.93437143919824</v>
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06291741386821</v>
+        <v>18.07580714662249</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8390326523783</v>
+        <v>117.9231228136801</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881111395759318</v>
+        <v>6.886021770141901</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.332673603019426</v>
+        <v>5.575345212417637</v>
       </c>
       <c r="C2" t="n">
-        <v>14.03113818909541</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="D2" t="n">
-        <v>37.96712896633689</v>
+        <v>32.60973174426206</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.9280957378785</v>
+        <v>15.41343895667492</v>
       </c>
       <c r="C3" t="n">
-        <v>26.64463269325843</v>
+        <v>18.74647241259284</v>
       </c>
       <c r="D3" t="n">
-        <v>57.19171251089794</v>
+        <v>54.80115685105696</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.83923972287755</v>
+        <v>23.66208316775662</v>
       </c>
       <c r="C4" t="n">
-        <v>49.58316780298516</v>
+        <v>35.51865019194535</v>
       </c>
       <c r="D4" t="n">
-        <v>53.79486545420397</v>
+        <v>43.64850293081319</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.26804248545517</v>
+        <v>22.18749811597792</v>
       </c>
       <c r="C5" t="n">
-        <v>39.83441309981433</v>
+        <v>38.16544200259476</v>
       </c>
       <c r="D5" t="n">
-        <v>33.74757733348411</v>
+        <v>31.56318869153496</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.97361598517235</v>
+        <v>13.04153650321463</v>
       </c>
       <c r="C6" t="n">
-        <v>20.12582793705961</v>
+        <v>23.78872862160447</v>
       </c>
       <c r="D6" t="n">
-        <v>31.23528495831652</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>14.73210604992764</v>
+        <v>16.10949807898591</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>22.18749811597791</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.060196626808141</v>
+        <v>7.068121221523376</v>
       </c>
       <c r="C21" t="n">
-        <v>66.18934337632632</v>
+        <v>67.14715160447207</v>
       </c>
       <c r="D21" t="n">
-        <v>5.295147470106106</v>
+        <v>5.301090916142533</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.787803627162447</v>
+        <v>5.721625620350411</v>
       </c>
       <c r="C2" t="n">
-        <v>6.185992284459152</v>
+        <v>3.333033455917921</v>
       </c>
       <c r="D2" t="n">
-        <v>32.40160123096173</v>
+        <v>29.35720160009237</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.28214680621311</v>
+        <v>18.07888397370501</v>
       </c>
       <c r="C3" t="n">
-        <v>44.82169143738813</v>
+        <v>16.92533042121501</v>
       </c>
       <c r="D3" t="n">
-        <v>75.26568774608171</v>
+        <v>69.72863069412971</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.2551408965797</v>
+        <v>28.10350978176919</v>
       </c>
       <c r="C4" t="n">
-        <v>60.45700537522283</v>
+        <v>43.02312964320797</v>
       </c>
       <c r="D4" t="n">
-        <v>70.76928326063133</v>
+        <v>63.18822748843746</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.77274292089604</v>
+        <v>30.40963513904496</v>
       </c>
       <c r="C5" t="n">
-        <v>71.49577656177398</v>
+        <v>55.59146375297565</v>
       </c>
       <c r="D5" t="n">
-        <v>46.75573441475435</v>
+        <v>40.84070449666732</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.4113776502752</v>
+        <v>22.94344384824796</v>
       </c>
       <c r="C6" t="n">
-        <v>45.44411948188061</v>
+        <v>46.20890094348888</v>
       </c>
       <c r="D6" t="n">
-        <v>35.38120551335081</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.87562114119692</v>
+        <v>11.5581157220977</v>
       </c>
       <c r="C7" t="n">
-        <v>23.05634483423634</v>
+        <v>27.24840753137022</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>33.65627479698915</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>19.61041039233004</v>
+        <v>20.69524160552276</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
         <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
         <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.281325811302288</v>
+        <v>7.295406918709213</v>
       </c>
       <c r="C21" t="n">
-        <v>75.54375529226125</v>
+        <v>77.51369851128538</v>
       </c>
       <c r="D21" t="n">
-        <v>6.371160084889502</v>
+        <v>6.383481053870561</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.127087422204344</v>
+        <v>5.325981295538947</v>
       </c>
       <c r="C2" t="n">
-        <v>4.636794407157685</v>
+        <v>3.645229225868407</v>
       </c>
       <c r="D2" t="n">
-        <v>36.41793108903543</v>
+        <v>22.26603793231766</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.41959148480766</v>
+        <v>19.1440802328128</v>
       </c>
       <c r="C3" t="n">
-        <v>32.42221793275092</v>
+        <v>14.62804079327748</v>
       </c>
       <c r="D3" t="n">
-        <v>83.72344421816798</v>
+        <v>78.21093085882215</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.73860273542564</v>
+        <v>32.22586839190155</v>
       </c>
       <c r="C4" t="n">
-        <v>89.83678717251287</v>
+        <v>42.27012915405066</v>
       </c>
       <c r="D4" t="n">
-        <v>92.59353472603793</v>
+        <v>83.32779989335653</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.20948178056562</v>
+        <v>37.45367491701582</v>
       </c>
       <c r="C5" t="n">
-        <v>94.49321653375551</v>
+        <v>69.80226177194822</v>
       </c>
       <c r="D5" t="n">
-        <v>61.1628819745763</v>
+        <v>55.07604620824608</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.49316580936395</v>
+        <v>33.08686112852601</v>
       </c>
       <c r="C6" t="n">
-        <v>82.83790778893737</v>
+        <v>70.23913950033806</v>
       </c>
       <c r="D6" t="n">
-        <v>42.38499363544755</v>
+        <v>39.64788103600744</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.35577788403162</v>
+        <v>20.48122060599696</v>
       </c>
       <c r="C7" t="n">
-        <v>46.17257627843174</v>
+        <v>49.58611304609789</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>36.59071868498287</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>29.37389131106456</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>24.62812290873548</v>
+        <v>25.4046853427947</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.488644421333814</v>
+        <v>7.511878304773352</v>
       </c>
       <c r="C21" t="n">
-        <v>85.18333029267214</v>
+        <v>87.3255852929902</v>
       </c>
       <c r="D21" t="n">
-        <v>7.488644421333814</v>
+        <v>7.511878304773352</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_43_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_43_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497636160854</v>
+        <v>10.84497648462255</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907204433041</v>
+        <v>37.78907247296991</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.508586368528853</v>
+        <v>1.371501542832794</v>
       </c>
       <c r="C2" t="n">
-        <v>4.396266219617217</v>
+        <v>3.044399630869359</v>
       </c>
       <c r="D2" t="n">
-        <v>23.43431770037136</v>
+        <v>19.57310397956866</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.6532063806894</v>
+        <v>9.900925597329083</v>
       </c>
       <c r="C3" t="n">
-        <v>14.34824269756713</v>
+        <v>31.24412068765474</v>
       </c>
       <c r="D3" t="n">
-        <v>77.73478322226245</v>
+        <v>80.91073704550088</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.75288698263284</v>
+        <v>14.9579080219044</v>
       </c>
       <c r="C4" t="n">
-        <v>39.06668639509333</v>
+        <v>71.93069079475531</v>
       </c>
       <c r="D4" t="n">
-        <v>101.8847949990297</v>
+        <v>87.06727689883262</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.6632291463769</v>
+        <v>14.08807955594173</v>
       </c>
       <c r="C5" t="n">
-        <v>74.39193228930206</v>
+        <v>76.79721416470676</v>
       </c>
       <c r="D5" t="n">
-        <v>72.57569903644547</v>
+        <v>49.5291716792516</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.38499363544755</v>
+        <v>10.06291396852981</v>
       </c>
       <c r="C6" t="n">
-        <v>91.25050386662829</v>
+        <v>58.20389439397641</v>
       </c>
       <c r="D6" t="n">
-        <v>47.81896717845365</v>
+        <v>30.71201343195298</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.72183090899544</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>77.49327328701773</v>
+        <v>37.18958478457343</v>
       </c>
       <c r="D7" t="n">
-        <v>39.58504918293564</v>
+        <v>29.46421209985527</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.10557108816892</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>48.81740459367264</v>
+        <v>28.78975142703771</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.987499321752047</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>38.15071578703105</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>28.42257778564941</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.716697278998705</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96.45871598748383</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.681284438873544</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.658212930201868</v>
+        <v>1.52367243699105</v>
       </c>
       <c r="C2" t="n">
-        <v>8.497026380256143</v>
+        <v>8.532369297609028</v>
       </c>
       <c r="D2" t="n">
-        <v>25.12685074249287</v>
+        <v>21.33534110869168</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.59430151843459</v>
+        <v>7.073492209098269</v>
       </c>
       <c r="C3" t="n">
-        <v>15.79141182280995</v>
+        <v>19.47787445225672</v>
       </c>
       <c r="D3" t="n">
-        <v>78.06366870318513</v>
+        <v>77.79368808451726</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.35273482992764</v>
+        <v>17.53597749325653</v>
       </c>
       <c r="C4" t="n">
-        <v>37.35648189429538</v>
+        <v>76.38488012892309</v>
       </c>
       <c r="D4" t="n">
-        <v>116.102465251932</v>
+        <v>108.0874769944611</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.71293842639499</v>
+        <v>18.70229376590174</v>
       </c>
       <c r="C5" t="n">
-        <v>73.18929135159972</v>
+        <v>108.9985388640021</v>
       </c>
       <c r="D5" t="n">
-        <v>89.78082755337083</v>
+        <v>69.50773746067419</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.59633143376788</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="C6" t="n">
-        <v>103.8895238111017</v>
+        <v>92.57880851047423</v>
       </c>
       <c r="D6" t="n">
-        <v>58.76741757621409</v>
+        <v>39.28561613314037</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.90255460203486</v>
+        <v>8.92310488389926</v>
       </c>
       <c r="C7" t="n">
-        <v>104.8614540383061</v>
+        <v>61.74309486778615</v>
       </c>
       <c r="D7" t="n">
-        <v>43.71722527011047</v>
+        <v>31.68001666834032</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.36697801940583</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>74.93680226515903</v>
+        <v>39.63806355896497</v>
       </c>
       <c r="D8" t="n">
-        <v>39.05392367493811</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.98124898262807</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>46.26093357181394</v>
+        <v>35.49999698556465</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>35.3036474447153</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.61999118966103</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.908697058462047</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105.7788231569299</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.885871323077559</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.506843857298612</v>
+        <v>0.7824529202847079</v>
       </c>
       <c r="C2" t="n">
-        <v>9.322676199527711</v>
+        <v>3.437098712568083</v>
       </c>
       <c r="D2" t="n">
-        <v>23.23109592559227</v>
+        <v>14.38751260573701</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.26327261565417</v>
+        <v>7.01458734684346</v>
       </c>
       <c r="C3" t="n">
-        <v>24.38170423496954</v>
+        <v>27.90617849321558</v>
       </c>
       <c r="D3" t="n">
-        <v>79.28594459497242</v>
+        <v>79.37430188835462</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.25063306868597</v>
+        <v>19.32275831498572</v>
       </c>
       <c r="C4" t="n">
-        <v>38.31368590593603</v>
+        <v>71.73924999242718</v>
       </c>
       <c r="D4" t="n">
-        <v>126.746573861376</v>
+        <v>120.8374344295144</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.92187076095032</v>
+        <v>18.92318699935727</v>
       </c>
       <c r="C5" t="n">
-        <v>70.34222300928397</v>
+        <v>133.3213382367169</v>
       </c>
       <c r="D5" t="n">
-        <v>106.6914317590221</v>
+        <v>80.79783605951251</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.91584140600459</v>
+        <v>12.15600007398401</v>
       </c>
       <c r="C6" t="n">
-        <v>110.0077755039679</v>
+        <v>123.572583533546</v>
       </c>
       <c r="D6" t="n">
-        <v>71.56744414418399</v>
+        <v>39.60762938013333</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>50.2448657556475</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>125.2229014243849</v>
+        <v>62.04252791758142</v>
       </c>
       <c r="D7" t="n">
-        <v>49.22679338634357</v>
+        <v>33.65627479698915</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.21252483466959</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>104.8948334602505</v>
+        <v>40.88979188187965</v>
       </c>
       <c r="D8" t="n">
-        <v>41.80772598535042</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.52812351162255</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>67.22811929141305</v>
+        <v>26.95781021091316</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>43.70249905454677</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>37.15424186722054</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.7169632282032</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>30.91916219754903</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>31.73990327829938</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.087136003923183</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>114.2307960554149</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.11981200539437</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.609526455617027</v>
+        <v>0.7294385442553801</v>
       </c>
       <c r="C2" t="n">
-        <v>6.115306449753382</v>
+        <v>5.364269456004572</v>
       </c>
       <c r="D2" t="n">
-        <v>18.85544640776424</v>
+        <v>14.4964866009084</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.84312565596554</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C3" t="n">
-        <v>35.63253292563798</v>
+        <v>19.35515598922587</v>
       </c>
       <c r="D3" t="n">
-        <v>88.799079849124</v>
+        <v>72.65423885278521</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.98115117163684</v>
+        <v>16.69363796301277</v>
       </c>
       <c r="C4" t="n">
-        <v>57.54710517983528</v>
+        <v>71.38189382808135</v>
       </c>
       <c r="D4" t="n">
-        <v>122.9815714155894</v>
+        <v>132.7578150544792</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.05406254365837</v>
+        <v>23.97918767622835</v>
       </c>
       <c r="C5" t="n">
-        <v>65.72800879932397</v>
+        <v>135.505726878666</v>
       </c>
       <c r="D5" t="n">
-        <v>72.45298057341462</v>
+        <v>105.2924412804704</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.19503330244241</v>
+        <v>18.23400011097601</v>
       </c>
       <c r="C6" t="n">
-        <v>82.47564288607032</v>
+        <v>169.0972063271749</v>
       </c>
       <c r="D6" t="n">
-        <v>32.40258297866598</v>
+        <v>53.33344403320799</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.97838585497334</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>73.72041685959724</v>
+        <v>119.2941270384384</v>
       </c>
       <c r="D7" t="n">
-        <v>29.34443887993716</v>
+        <v>37.30935800449154</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.10004045484194</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>49.48499303256047</v>
+        <v>61.2512392679585</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>33.28124717396686</v>
+        <v>37.94062177832222</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
+        <v>21.51009220004762</v>
+      </c>
+      <c r="D14" t="n">
         <v>21.20280516861837</v>
-      </c>
-      <c r="D14" t="n">
-        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.502294971675872</v>
+        <v>0.3868085954732433</v>
       </c>
       <c r="C2" t="n">
-        <v>2.716495897650924</v>
+        <v>2.746930076482576</v>
       </c>
       <c r="D2" t="n">
-        <v>13.95063487734718</v>
+        <v>10.73344765053038</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.32556468937822</v>
+        <v>3.774819922828986</v>
       </c>
       <c r="C3" t="n">
-        <v>29.96784867213389</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D3" t="n">
-        <v>85.18133955897451</v>
+        <v>69.021772347072</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.71459882216722</v>
+        <v>13.98794129010856</v>
       </c>
       <c r="C4" t="n">
-        <v>75.73398140100744</v>
+        <v>61.83537915198535</v>
       </c>
       <c r="D4" t="n">
-        <v>136.9950381460084</v>
+        <v>138.6159036057199</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.76016012719008</v>
+        <v>25.86905200690346</v>
       </c>
       <c r="C5" t="n">
-        <v>86.9092155184489</v>
+        <v>138.6473195322558</v>
       </c>
       <c r="D5" t="n">
-        <v>93.6832746777519</v>
+        <v>124.26471566504</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.0315234041897</v>
+        <v>22.86294053649972</v>
       </c>
       <c r="C6" t="n">
-        <v>95.87944429215202</v>
+        <v>197.5148753743031</v>
       </c>
       <c r="D6" t="n">
-        <v>42.0629803884546</v>
+        <v>66.29447722467438</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.43940636534185</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>94.56095712534852</v>
+        <v>167.5627346654371</v>
       </c>
       <c r="D7" t="n">
-        <v>32.33876937788993</v>
+        <v>41.9206269713388</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>65.92435834017331</v>
+        <v>89.20650514638642</v>
       </c>
       <c r="D8" t="n">
-        <v>28.53940576245478</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>40.38124657107979</v>
+        <v>49.81093327037041</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>30.74146586308036</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.490513999224911</v>
+        <v>1.267436286182632</v>
       </c>
       <c r="C2" t="n">
-        <v>5.537057051952011</v>
+        <v>7.7410806479861</v>
       </c>
       <c r="D2" t="n">
-        <v>18.39697022988098</v>
+        <v>12.42892593576462</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.66088043587412</v>
+        <v>2.528000338435537</v>
       </c>
       <c r="C3" t="n">
-        <v>19.20789383358884</v>
+        <v>15.13364086096458</v>
       </c>
       <c r="D3" t="n">
-        <v>77.65624340592271</v>
+        <v>62.72386082432871</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.09970596413923</v>
+        <v>10.65687132959913</v>
       </c>
       <c r="C4" t="n">
-        <v>75.28728619557515</v>
+        <v>56.20701956353839</v>
       </c>
       <c r="D4" t="n">
-        <v>147.4221805128138</v>
+        <v>139.726260259223</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.78594760940775</v>
+        <v>24.22462460229005</v>
       </c>
       <c r="C5" t="n">
-        <v>115.2326367859694</v>
+        <v>127.6026578594792</v>
       </c>
       <c r="D5" t="n">
-        <v>118.5214915951962</v>
+        <v>143.7033202091269</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.82776185006286</v>
+        <v>28.41766904712818</v>
       </c>
       <c r="C6" t="n">
-        <v>116.810305346694</v>
+        <v>209.0268489543012</v>
       </c>
       <c r="D6" t="n">
-        <v>58.6064109527176</v>
+        <v>86.50080847348222</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.4404702285041</v>
+        <v>16.88802400845363</v>
       </c>
       <c r="C7" t="n">
-        <v>117.5574153496258</v>
+        <v>224.8143337862941</v>
       </c>
       <c r="D7" t="n">
-        <v>36.4110588551057</v>
+        <v>49.82565948593412</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.43798264928109</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>94.88100687693299</v>
+        <v>149.3729132011522</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45872252425729</v>
+        <v>42.55876297909923</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>60.12811989430013</v>
+        <v>76.54686850012379</v>
       </c>
       <c r="D9" t="n">
-        <v>30.50780990946962</v>
+        <v>42.71093387325747</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.131775176547325</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>39.00483628972578</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47308888692249</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>30.56376952861169</v>
+        <v>33.7623035490478</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.03256190515617</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>42.98484148274235</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.59770442543706</v>
+        <v>0.8413577825395164</v>
       </c>
       <c r="C2" t="n">
-        <v>2.455351008321272</v>
+        <v>3.963315482044373</v>
       </c>
       <c r="D2" t="n">
-        <v>12.68516208657304</v>
+        <v>8.949612071913924</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.53325323432204</v>
+        <v>4.0938879267092</v>
       </c>
       <c r="C3" t="n">
-        <v>21.39719121405923</v>
+        <v>23.05634483423634</v>
       </c>
       <c r="D3" t="n">
-        <v>77.3960802642973</v>
+        <v>67.1613604475243</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.82191242156638</v>
+        <v>16.84679060487526</v>
       </c>
       <c r="C4" t="n">
-        <v>72.41567416065323</v>
+        <v>76.67842269249287</v>
       </c>
       <c r="D4" t="n">
-        <v>155.2457279679566</v>
+        <v>144.7675347205304</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.19122948481243</v>
+        <v>18.01507037292897</v>
       </c>
       <c r="C5" t="n">
-        <v>136.8065425867931</v>
+        <v>183.0468594568178</v>
       </c>
       <c r="D5" t="n">
-        <v>128.1671627894211</v>
+        <v>132.4132216102886</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.71580155404972</v>
+        <v>10.465430527271</v>
       </c>
       <c r="C6" t="n">
-        <v>150.9437095279471</v>
+        <v>203.3513654760503</v>
       </c>
       <c r="D6" t="n">
-        <v>57.43911293236815</v>
+        <v>71.96996070292518</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.18072369303942</v>
+        <v>4.371722527011046</v>
       </c>
       <c r="C7" t="n">
-        <v>125.8217675239755</v>
+        <v>105.0411138681832</v>
       </c>
       <c r="D7" t="n">
-        <v>36.29128563518759</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>75.93818492349078</v>
+        <v>56.41122308602172</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>21.67895280517806</v>
+        <v>21.85664913964673</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>36.19212911705866</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.246058820867455</v>
+        <v>0.4329507375728434</v>
       </c>
       <c r="C2" t="n">
-        <v>1.88986433067511</v>
+        <v>2.482839944040183</v>
       </c>
       <c r="D2" t="n">
-        <v>17.33373746618168</v>
+        <v>6.796639356500669</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.71639808665969</v>
+        <v>3.475386873033709</v>
       </c>
       <c r="C3" t="n">
-        <v>15.06491852166731</v>
+        <v>18.84955592153876</v>
       </c>
       <c r="D3" t="n">
-        <v>70.05751617505238</v>
+        <v>59.11593801122169</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.36321525950487</v>
+        <v>11.70341438232623</v>
       </c>
       <c r="C4" t="n">
-        <v>62.52456604036662</v>
+        <v>64.52831310473435</v>
       </c>
       <c r="D4" t="n">
-        <v>159.9551717052286</v>
+        <v>139.5348194568949</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.92311455056183</v>
+        <v>17.00877897607599</v>
       </c>
       <c r="C5" t="n">
-        <v>136.4383871977005</v>
+        <v>145.8386214658637</v>
       </c>
       <c r="D5" t="n">
-        <v>150.4282919832175</v>
+        <v>137.0519795128548</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.50324532831367</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C6" t="n">
-        <v>185.5198819238155</v>
+        <v>203.914888658288</v>
       </c>
       <c r="D6" t="n">
-        <v>78.65173557802898</v>
+        <v>78.77249054565134</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.15804568485051</v>
+        <v>3.712969817461437</v>
       </c>
       <c r="C7" t="n">
-        <v>168.580807034741</v>
+        <v>138.1584091755409</v>
       </c>
       <c r="D7" t="n">
-        <v>42.99858595060179</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.842781498600267</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>117.0783224699534</v>
+        <v>61.58503348740241</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>54.91405783704532</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>21.63281066307846</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>19.21771131063132</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>20.21418523044183</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.58827216348886</v>
+        <v>14.03801042302514</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>22.34752299177014</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.029673415305656</v>
+        <v>0.4840016181936775</v>
       </c>
       <c r="C2" t="n">
-        <v>2.310052348092745</v>
+        <v>6.78976712257094</v>
       </c>
       <c r="D2" t="n">
-        <v>12.60073178400781</v>
+        <v>6.842781498600268</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.85384276525424</v>
+        <v>2.385646921319749</v>
       </c>
       <c r="C3" t="n">
-        <v>11.43736075447534</v>
+        <v>13.27813769993811</v>
       </c>
       <c r="D3" t="n">
-        <v>68.25600913775949</v>
+        <v>50.83489612589984</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.10497455555895</v>
+        <v>9.074294030353268</v>
       </c>
       <c r="C4" t="n">
-        <v>52.71003424101125</v>
+        <v>54.39471330149878</v>
       </c>
       <c r="D4" t="n">
-        <v>159.8147817835213</v>
+        <v>138.0032930382699</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.64179492779949</v>
+        <v>17.76963344686727</v>
       </c>
       <c r="C5" t="n">
-        <v>132.4623089955009</v>
+        <v>132.2905031472577</v>
       </c>
       <c r="D5" t="n">
-        <v>168.3451875857218</v>
+        <v>156.8096520608218</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.43911293236815</v>
+        <v>16.98619877887832</v>
       </c>
       <c r="C6" t="n">
-        <v>206.0482264196164</v>
+        <v>221.9073788340193</v>
       </c>
       <c r="D6" t="n">
-        <v>95.35617276578846</v>
+        <v>102.8832324142488</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.27781890476862</v>
+        <v>8.024805734513427</v>
       </c>
       <c r="C7" t="n">
-        <v>209.5432482467349</v>
+        <v>220.6821576991193</v>
       </c>
       <c r="D7" t="n">
-        <v>49.76577287597506</v>
+        <v>50.18497914568845</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>150.04050164004</v>
+        <v>125.0059351817464</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>69.33593161243097</v>
+        <v>54.0265579124062</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>23.74062298409636</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>28.04362317181014</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>20.92595231602077</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.23287949455151</v>
+        <v>17.94732978133594</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.245077073163208</v>
+        <v>0.4702571503342222</v>
       </c>
       <c r="C2" t="n">
-        <v>5.648976290236146</v>
+        <v>14.14894791360503</v>
       </c>
       <c r="D2" t="n">
-        <v>14.88133170097315</v>
+        <v>14.5445922384165</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.56637061435917</v>
+        <v>1.988039101099791</v>
       </c>
       <c r="C3" t="n">
-        <v>10.14145378486955</v>
+        <v>20.52834449580081</v>
       </c>
       <c r="D3" t="n">
-        <v>63.10183369046374</v>
+        <v>44.93950116189774</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.15303913533804</v>
+        <v>6.777004402415732</v>
       </c>
       <c r="C4" t="n">
-        <v>41.01938257884023</v>
+        <v>42.95931604243193</v>
       </c>
       <c r="D4" t="n">
-        <v>157.657882077291</v>
+        <v>131.4687803188031</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.87464906015524</v>
+        <v>15.90431280879833</v>
       </c>
       <c r="C5" t="n">
-        <v>117.2452195796754</v>
+        <v>114.4472386225719</v>
       </c>
       <c r="D5" t="n">
-        <v>183.218665305061</v>
+        <v>170.7995568463388</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69.39385472698156</v>
+        <v>20.68935111929729</v>
       </c>
       <c r="C6" t="n">
-        <v>208.7853390190565</v>
+        <v>217.1174317849991</v>
       </c>
       <c r="D6" t="n">
-        <v>117.4543318406799</v>
+        <v>126.6317093799791</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.28561613314036</v>
+        <v>13.89369351050086</v>
       </c>
       <c r="C7" t="n">
-        <v>248.4096581101619</v>
+        <v>273.1428280232518</v>
       </c>
       <c r="D7" t="n">
-        <v>61.86286808770426</v>
+        <v>65.27640485537042</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>205.700687732313</v>
+        <v>208.9551813718911</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.217187226816797</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>115.8187401654047</v>
+        <v>103.393741220457</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61249706092553</v>
+        <v>25.95937279569415</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>51.38958357879929</v>
+        <v>45.41074005993622</v>
       </c>
       <c r="D10" t="n">
-        <v>27.18950266911542</v>
+        <v>21.78007281871549</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>17.17076734727672</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.765804267041517</v>
+        <v>3.100359250011427</v>
       </c>
       <c r="C2" t="n">
-        <v>3.257438882690916</v>
+        <v>7.528041396164542</v>
       </c>
       <c r="D2" t="n">
-        <v>7.823547455142832</v>
+        <v>8.01204301435822</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.938370878810703</v>
+        <v>1.180060740504666</v>
       </c>
       <c r="C2" t="n">
-        <v>3.073852061996763</v>
+        <v>12.16581755102647</v>
       </c>
       <c r="D2" t="n">
-        <v>10.83358591636355</v>
+        <v>11.92823460659875</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.99896149903352</v>
+        <v>1.767145867644259</v>
       </c>
       <c r="C3" t="n">
-        <v>15.59997102048182</v>
+        <v>37.7825603979385</v>
       </c>
       <c r="D3" t="n">
-        <v>69.4242889058132</v>
+        <v>45.69544689416779</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.85194568977053</v>
+        <v>5.322054304721959</v>
       </c>
       <c r="C4" t="n">
-        <v>59.89544568839366</v>
+        <v>46.54564040604553</v>
       </c>
       <c r="D4" t="n">
-        <v>164.2179202370682</v>
+        <v>125.0746575210436</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.5096755938869</v>
+        <v>13.42539985557513</v>
       </c>
       <c r="C5" t="n">
-        <v>175.9782759862408</v>
+        <v>97.38937226128361</v>
       </c>
       <c r="D5" t="n">
-        <v>168.0506632744478</v>
+        <v>176.5427809161827</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.39250345971625</v>
+        <v>21.17237098978672</v>
       </c>
       <c r="C6" t="n">
-        <v>210.6771668451401</v>
+        <v>202.0230608322044</v>
       </c>
       <c r="D6" t="n">
-        <v>93.7461065308237</v>
+        <v>148.4883585196258</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.905032514595317</v>
+        <v>18.86428213710246</v>
       </c>
       <c r="C7" t="n">
-        <v>144.6261630511189</v>
+        <v>291.8274503304771</v>
       </c>
       <c r="D7" t="n">
-        <v>36.9500383447372</v>
+        <v>82.70340835345554</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.169662426385451</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>85.36787162278139</v>
+        <v>281.1381813266378</v>
       </c>
       <c r="D8" t="n">
-        <v>25.45180923259856</v>
+        <v>43.30979997284804</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>173.3952977763673</v>
       </c>
       <c r="D9" t="n">
-        <v>20.74531073843935</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>23.77302065833652</v>
+        <v>78.29437941368313</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.41424077792992</v>
+        <v>36.42774856607789</v>
       </c>
       <c r="D11" t="n">
-        <v>17.05884810899257</v>
+        <v>19.90198946049134</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>13.88583952886689</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.40652566501619</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.56494689829842</v>
+        <v>4.040873550679871</v>
       </c>
       <c r="C2" t="n">
-        <v>3.517602024316322</v>
+        <v>5.472261703471721</v>
       </c>
       <c r="D2" t="n">
-        <v>17.84424627239003</v>
+        <v>17.6528054700619</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.24730261047896</v>
+        <v>5.129631754689584</v>
       </c>
       <c r="C3" t="n">
-        <v>8.33503800905542</v>
+        <v>14.86366024229671</v>
       </c>
       <c r="D3" t="n">
-        <v>10.0187353218387</v>
+        <v>8.511752595819846</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39911120893886</v>
+        <v>11.67856102018222</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14828809385637</v>
+        <v>59.94994657026874</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576366024581042</v>
+        <v>0.7785707346788149</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.903829782712818</v>
+        <v>2.518182861393068</v>
       </c>
       <c r="C2" t="n">
-        <v>6.253732876052181</v>
+        <v>3.122939447209104</v>
       </c>
       <c r="D2" t="n">
-        <v>21.01038261858599</v>
+        <v>23.79265561242145</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.50103548653114</v>
+        <v>10.73541114593887</v>
       </c>
       <c r="C3" t="n">
-        <v>11.76133749687679</v>
+        <v>19.21771131063132</v>
       </c>
       <c r="D3" t="n">
-        <v>22.58510593619787</v>
+        <v>21.90770002026757</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.25595841336793</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C4" t="n">
-        <v>13.4519070435898</v>
+        <v>24.72138894063893</v>
       </c>
       <c r="D4" t="n">
-        <v>20.31825048709199</v>
+        <v>18.65909686691488</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>21.07812321017901</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44433458296807</v>
+        <v>13.63125812962905</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16312977866396</v>
+        <v>73.76916164269839</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251438859572225</v>
+        <v>1.603677427015183</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.017712516405448</v>
+        <v>1.533489914033518</v>
       </c>
       <c r="C2" t="n">
-        <v>4.580834788015617</v>
+        <v>2.898119222936584</v>
       </c>
       <c r="D2" t="n">
-        <v>23.49911304885165</v>
+        <v>29.6095107600838</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.64691498383642</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="C3" t="n">
-        <v>19.38460842035327</v>
+        <v>14.69185439405352</v>
       </c>
       <c r="D3" t="n">
-        <v>34.1500938922253</v>
+        <v>36.59955441432109</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.39330528097125</v>
+        <v>15.07277250330128</v>
       </c>
       <c r="C4" t="n">
-        <v>22.74316731658161</v>
+        <v>39.47509344006</v>
       </c>
       <c r="D4" t="n">
-        <v>27.0697294491973</v>
+        <v>25.62754207165874</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.73817646260237</v>
+        <v>6.553165925847461</v>
       </c>
       <c r="C5" t="n">
-        <v>16.66516727958961</v>
+        <v>29.82058651649687</v>
       </c>
       <c r="D5" t="n">
-        <v>29.74695543867836</v>
+        <v>26.80171232593793</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>24.18437294641592</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74233284203892</v>
+        <v>14.84504617237262</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1282303364374</v>
+        <v>87.42082745952767</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022699852611676</v>
+        <v>2.474174362062104</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.994150571503524</v>
+        <v>2.572178985126643</v>
       </c>
       <c r="C2" t="n">
-        <v>5.400594121061704</v>
+        <v>4.496404485450391</v>
       </c>
       <c r="D2" t="n">
-        <v>31.20681427489336</v>
+        <v>26.60928977590555</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.40147805777471</v>
+        <v>7.166758241001716</v>
       </c>
       <c r="C3" t="n">
-        <v>18.44213062427633</v>
+        <v>12.59582304548658</v>
       </c>
       <c r="D3" t="n">
-        <v>44.4142661401257</v>
+        <v>51.79210013754048</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.51566389110361</v>
+        <v>17.33177397077319</v>
       </c>
       <c r="C4" t="n">
-        <v>37.39477005476101</v>
+        <v>37.91804158112456</v>
       </c>
       <c r="D4" t="n">
-        <v>37.24161741289851</v>
+        <v>37.94356702143497</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.48264432205772</v>
+        <v>15.04528356758237</v>
       </c>
       <c r="C5" t="n">
-        <v>30.60598467989432</v>
+        <v>54.85515297479054</v>
       </c>
       <c r="D5" t="n">
-        <v>32.88854809226815</v>
+        <v>30.2869166760141</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.55222523587222</v>
+        <v>6.923284810348508</v>
       </c>
       <c r="C6" t="n">
-        <v>19.64280806657019</v>
+        <v>30.95352336719769</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>33.85164259013428</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07580714662249</v>
+        <v>16.09358126061185</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9231228136801</v>
+        <v>101.6436711196538</v>
       </c>
       <c r="D21" t="n">
-        <v>6.886021770141901</v>
+        <v>3.388122370655127</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.575345212417637</v>
+        <v>1.697441780642735</v>
       </c>
       <c r="C2" t="n">
-        <v>4.088979188187965</v>
+        <v>4.586725274241098</v>
       </c>
       <c r="D2" t="n">
-        <v>32.60973174426206</v>
+        <v>27.52329688855933</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.41343895667492</v>
+        <v>8.109236037078654</v>
       </c>
       <c r="C3" t="n">
-        <v>18.74647241259284</v>
+        <v>15.44780012632356</v>
       </c>
       <c r="D3" t="n">
-        <v>54.80115685105696</v>
+        <v>60.49529353568845</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.66208316775662</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="C4" t="n">
-        <v>35.51865019194535</v>
+        <v>33.93607289269949</v>
       </c>
       <c r="D4" t="n">
-        <v>43.64850293081319</v>
+        <v>54.06288257746336</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.18749811597792</v>
+        <v>20.69033286700153</v>
       </c>
       <c r="C5" t="n">
-        <v>38.16544200259476</v>
+        <v>63.42090169434396</v>
       </c>
       <c r="D5" t="n">
-        <v>31.56318869153496</v>
+        <v>37.13460691313561</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.04153650321463</v>
+        <v>13.88682127657114</v>
       </c>
       <c r="C6" t="n">
-        <v>23.78872862160447</v>
+        <v>61.18251692866124</v>
       </c>
       <c r="D6" t="n">
-        <v>30.79251674370121</v>
+        <v>35.783722072092</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>16.10949807898591</v>
+        <v>32.03933632809466</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.068121221523376</v>
+        <v>17.37258863637838</v>
       </c>
       <c r="C21" t="n">
-        <v>67.14715160447207</v>
+        <v>115.5277144319162</v>
       </c>
       <c r="D21" t="n">
-        <v>5.301090916142533</v>
+        <v>4.343147159094595</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.721625620350411</v>
+        <v>3.048326621686346</v>
       </c>
       <c r="C2" t="n">
-        <v>3.333033455917921</v>
+        <v>12.2669375645639</v>
       </c>
       <c r="D2" t="n">
-        <v>29.35720160009237</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.07888397370501</v>
+        <v>6.852598975642737</v>
       </c>
       <c r="C3" t="n">
-        <v>16.92533042121501</v>
+        <v>16.76334205001429</v>
       </c>
       <c r="D3" t="n">
-        <v>69.72863069412971</v>
+        <v>68.53580723346982</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.10350978176919</v>
+        <v>15.50670498857837</v>
       </c>
       <c r="C4" t="n">
-        <v>43.02312964320797</v>
+        <v>36.51414236405162</v>
       </c>
       <c r="D4" t="n">
-        <v>63.18822748843746</v>
+        <v>69.73550292805943</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.40963513904496</v>
+        <v>22.31021657900877</v>
       </c>
       <c r="C5" t="n">
-        <v>55.59146375297565</v>
+        <v>63.02820261264524</v>
       </c>
       <c r="D5" t="n">
-        <v>40.84070449666732</v>
+        <v>47.5411325781518</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.94344384824796</v>
+        <v>20.7296027751714</v>
       </c>
       <c r="C6" t="n">
-        <v>46.20890094348888</v>
+        <v>81.46935148921733</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>39.04410619789565</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.5581157220977</v>
+        <v>12.03720860177014</v>
       </c>
       <c r="C7" t="n">
-        <v>27.24840753137022</v>
+        <v>60.30581622876881</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>20.69524160552276</v>
+        <v>33.79666471869644</v>
       </c>
       <c r="D8" t="n">
-        <v>31.87734795689393</v>
+        <v>39.22082078466007</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>46.7341359652609</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.295406918709213</v>
+        <v>18.67687136454797</v>
       </c>
       <c r="C21" t="n">
-        <v>77.51369851128538</v>
+        <v>128.9593498980693</v>
       </c>
       <c r="D21" t="n">
-        <v>6.383481053870561</v>
+        <v>5.336248961299421</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.325981295538947</v>
+        <v>2.636974333606933</v>
       </c>
       <c r="C2" t="n">
-        <v>3.645229225868407</v>
+        <v>7.35918079103409</v>
       </c>
       <c r="D2" t="n">
-        <v>22.26603793231766</v>
+        <v>27.19539315534089</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.1440802328128</v>
+        <v>9.925469289935252</v>
       </c>
       <c r="C3" t="n">
-        <v>14.62804079327748</v>
+        <v>32.80509953740717</v>
       </c>
       <c r="D3" t="n">
-        <v>78.21093085882215</v>
+        <v>76.52723354603887</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.22586839190155</v>
+        <v>10.70792221021996</v>
       </c>
       <c r="C4" t="n">
-        <v>42.27012915405066</v>
+        <v>54.94351026817274</v>
       </c>
       <c r="D4" t="n">
-        <v>83.32779989335653</v>
+        <v>64.56660126519998</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.45367491701582</v>
+        <v>11.65825398793088</v>
       </c>
       <c r="C5" t="n">
-        <v>69.80226177194822</v>
+        <v>48.67014243803564</v>
       </c>
       <c r="D5" t="n">
-        <v>55.07604620824608</v>
+        <v>37.47821860962199</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.08686112852601</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>70.23913950033806</v>
+        <v>39.68813269188156</v>
       </c>
       <c r="D6" t="n">
-        <v>39.64788103600744</v>
+        <v>25.96231803880691</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.48122060599696</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>49.58611304609789</v>
+        <v>23.71509754378595</v>
       </c>
       <c r="D7" t="n">
-        <v>36.59071868498287</v>
+        <v>27.5478405811655</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>29.37389131106456</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>25.4046853427947</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.511878304773352</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>87.3255852929902</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.511878304773352</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
